--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>Timestamp</t>
   </si>
@@ -113,6 +113,18 @@
   </si>
   <si>
     <t>+254720107685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eugene </t>
+  </si>
+  <si>
+    <t>Shem</t>
+  </si>
+  <si>
+    <t>eugeneshem43@gmail.com</t>
+  </si>
+  <si>
+    <t>0740228718</t>
   </si>
 </sst>
 </file>
@@ -276,38 +288,38 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF8F9FA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF442F65"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFF8F9FA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF8F9FA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF442F65"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFF8F9FA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -317,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -360,13 +372,16 @@
     <xf quotePrefix="1" borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="10" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf quotePrefix="1" borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -427,7 +442,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F7" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F8" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="6">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -762,20 +777,40 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14">
+      <c r="A7" s="7">
         <v>45729.54199271991</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="14" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15">
+        <v>45729.98487356481</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
   <si>
     <t>Timestamp</t>
   </si>
@@ -125,6 +125,84 @@
   </si>
   <si>
     <t>0740228718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stanley </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macharia </t>
+  </si>
+  <si>
+    <t>Mbatia</t>
+  </si>
+  <si>
+    <t>stanmacha625@gmail.com</t>
+  </si>
+  <si>
+    <t>0769994230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercy </t>
+  </si>
+  <si>
+    <t>Ndegwa</t>
+  </si>
+  <si>
+    <t>Waruguru</t>
+  </si>
+  <si>
+    <t>mercyndegwa832@gmail.com</t>
+  </si>
+  <si>
+    <t>0797152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antony </t>
+  </si>
+  <si>
+    <t>Mushiyii</t>
+  </si>
+  <si>
+    <t>musixi07@gmail.com</t>
+  </si>
+  <si>
+    <t>0717481072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eric </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mshephard </t>
+  </si>
+  <si>
+    <t>ercmshephard@gmail.com</t>
+  </si>
+  <si>
+    <t>0716290426</t>
+  </si>
+  <si>
+    <t>Brian</t>
+  </si>
+  <si>
+    <t>Towett</t>
+  </si>
+  <si>
+    <t>Briantowett2000@gmail.com</t>
+  </si>
+  <si>
+    <t>0712780716</t>
+  </si>
+  <si>
+    <t>Salome</t>
+  </si>
+  <si>
+    <t>Inyange</t>
+  </si>
+  <si>
+    <t>inyangesalome@gmail.com</t>
+  </si>
+  <si>
+    <t>0742439127</t>
   </si>
 </sst>
 </file>
@@ -442,7 +520,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F8" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F14" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="6">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -794,23 +872,132 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15">
+      <c r="A8" s="10">
         <v>45729.98487356481</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="13" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7">
+        <v>45736.66063238426</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10">
+        <v>45736.72968936343</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7">
+        <v>45736.73206912037</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10">
+        <v>45736.7642705787</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7">
+        <v>45736.95222440972</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15">
+        <v>45736.99910443287</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
   <si>
     <t>Timestamp</t>
   </si>
@@ -203,6 +203,21 @@
   </si>
   <si>
     <t>0742439127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mary Gloria </t>
+  </si>
+  <si>
+    <t>Kariuki</t>
+  </si>
+  <si>
+    <t>Njeri</t>
+  </si>
+  <si>
+    <t>mg.gatagia@gmail.com</t>
+  </si>
+  <si>
+    <t>0724105085</t>
   </si>
 </sst>
 </file>
@@ -366,38 +381,38 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF442F65"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF442F65"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -520,7 +535,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F14" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F15" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="6">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -983,21 +998,41 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15">
+      <c r="A14" s="10">
         <v>45736.99910443287</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16" t="s">
+      <c r="D14" s="11"/>
+      <c r="E14" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="13" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15">
+        <v>45737.32620246528</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="98">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,6 +31,12 @@
     <t>Phone Number</t>
   </si>
   <si>
+    <t>Feedback</t>
+  </si>
+  <si>
+    <t>Feedback Order</t>
+  </si>
+  <si>
     <t xml:space="preserve">STANLEY </t>
   </si>
   <si>
@@ -169,6 +175,11 @@
     <t>0717481072</t>
   </si>
   <si>
+    <t>Received,
+My feedback for now is it is so easy to use, 
+If I think of any other thing I'll be sharing</t>
+  </si>
+  <si>
     <t xml:space="preserve">Eric </t>
   </si>
   <si>
@@ -181,6 +192,11 @@
     <t>0716290426</t>
   </si>
   <si>
+    <t>So I have gone through the app, the experience for missions and signing up is very easier and the details of what is required to the point of showing weather it's very well detailed, I love it
+Learning tool that is amazing, can help track the progress of a missioner, and how involved they are on our material, is this where the current mizizi program will be put or incorporated or since it's not our manual it can't. We have our own discipleship material can it be placed here
+An addition is on the giving, the reason for giving, are only 3 on the drop down, you can add other so people can enter on their own what else they are giving for, esp the running of Tuesday fellowships</t>
+  </si>
+  <si>
     <t>Brian</t>
   </si>
   <si>
@@ -205,6 +221,9 @@
     <t>0742439127</t>
   </si>
   <si>
+    <t>Hey Miller, I've interacted with the app, it's pretty easy,keep up the great work.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mary Gloria </t>
   </si>
   <si>
@@ -218,6 +237,78 @@
   </si>
   <si>
     <t>0724105085</t>
+  </si>
+  <si>
+    <t>Esther</t>
+  </si>
+  <si>
+    <t>Nyokabi</t>
+  </si>
+  <si>
+    <t>Kabwere</t>
+  </si>
+  <si>
+    <t>18esthernyokabi@gmail.com</t>
+  </si>
+  <si>
+    <t>+254720482800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter </t>
+  </si>
+  <si>
+    <t>Gonzo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Namaba </t>
+  </si>
+  <si>
+    <t>petergonzonamaba@gmail.com</t>
+  </si>
+  <si>
+    <t>0706238192</t>
+  </si>
+  <si>
+    <t>Joshua</t>
+  </si>
+  <si>
+    <t>Mutua</t>
+  </si>
+  <si>
+    <t>Jaurumium@gmail.com</t>
+  </si>
+  <si>
+    <t>0727741208</t>
+  </si>
+  <si>
+    <t>Reena</t>
+  </si>
+  <si>
+    <t>Gakundi</t>
+  </si>
+  <si>
+    <t>Wambui</t>
+  </si>
+  <si>
+    <t>rewaga4@gmail.com</t>
+  </si>
+  <si>
+    <t>0714831056</t>
+  </si>
+  <si>
+    <t>Mary</t>
+  </si>
+  <si>
+    <t>Mutisya</t>
+  </si>
+  <si>
+    <t>Ndunge</t>
+  </si>
+  <si>
+    <t>mmutisya240@gmail.com</t>
+  </si>
+  <si>
+    <t>0791352339</t>
   </si>
 </sst>
 </file>
@@ -248,7 +339,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border/>
     <border>
       <left style="thin">
@@ -381,10 +472,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -392,27 +483,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF442F65"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFF8F9FA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -422,7 +499,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -432,6 +509,9 @@
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -441,7 +521,13 @@
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf quotePrefix="1" borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf quotePrefix="1" borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -450,7 +536,13 @@
     <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf quotePrefix="1" borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf quotePrefix="1" borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -459,22 +551,25 @@
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf quotePrefix="1" borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf quotePrefix="1" borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="10" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf quotePrefix="1" borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf quotePrefix="1" borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -535,14 +630,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F15" displayName="Form_Responses1" name="Form_Responses1" id="1">
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H20" displayName="Form_Responses1" name="Form_Responses1" id="1">
+  <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
     <tableColumn name="Last Name" id="3"/>
     <tableColumn name="Other Names" id="4"/>
     <tableColumn name="Email Address" id="5"/>
     <tableColumn name="Phone Number" id="6"/>
+    <tableColumn name="Feedback" id="7"/>
+    <tableColumn name="Feedback Order" id="8"/>
   </tableColumns>
   <tableStyleInfo name="Form Responses 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
@@ -749,7 +846,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="12" width="18.88"/>
+    <col customWidth="1" min="1" max="14" width="18.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -768,271 +865,416 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="4">
+      <c r="A2" s="5">
         <v>45728.821473171294</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="E2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="8"/>
+      <c r="H2" s="9"/>
     </row>
     <row r="3">
-      <c r="A3" s="7">
+      <c r="A3" s="10">
         <v>45729.213411793986</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="B3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="C3" s="11" t="s">
         <v>14</v>
       </c>
+      <c r="E3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4">
-      <c r="A4" s="10">
+      <c r="A4" s="15">
         <v>45729.26696155092</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="B4" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="C4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="D4" s="16" t="s">
         <v>19</v>
       </c>
+      <c r="E4" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="8"/>
+      <c r="H4" s="9"/>
     </row>
     <row r="5">
-      <c r="A5" s="7">
+      <c r="A5" s="10">
         <v>45729.32677667824</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="B5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="C5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="D5" s="11" t="s">
         <v>24</v>
       </c>
+      <c r="E5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="13"/>
+      <c r="H5" s="14"/>
     </row>
     <row r="6">
-      <c r="A6" s="10">
+      <c r="A6" s="15">
         <v>45729.53855537037</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="11" t="s">
+      <c r="B6" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="C6" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="D6" s="16" t="s">
         <v>29</v>
       </c>
+      <c r="E6" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="9"/>
     </row>
     <row r="7">
-      <c r="A7" s="7">
+      <c r="A7" s="10">
         <v>45729.54199271991</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="8" t="s">
+      <c r="B7" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="C7" s="11" t="s">
         <v>33</v>
       </c>
+      <c r="E7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="13"/>
+      <c r="H7" s="14"/>
     </row>
     <row r="8">
-      <c r="A8" s="10">
+      <c r="A8" s="15">
         <v>45729.98487356481</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="11" t="s">
+      <c r="B8" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="C8" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>37</v>
       </c>
+      <c r="E8" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="7">
+      <c r="A9" s="10">
         <v>45736.66063238426</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="B9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="C9" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="D9" s="11" t="s">
         <v>42</v>
       </c>
+      <c r="E9" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="14"/>
     </row>
     <row r="10">
-      <c r="A10" s="10">
+      <c r="A10" s="15">
         <v>45736.72968936343</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="11" t="s">
+      <c r="B10" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="C10" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="D10" s="16" t="s">
         <v>47</v>
       </c>
+      <c r="E10" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="8"/>
+      <c r="H10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="7">
+      <c r="A11" s="10">
         <v>45736.73206912037</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="8" t="s">
+      <c r="B11" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="C11" s="11" t="s">
         <v>51</v>
       </c>
+      <c r="E11" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="19">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="10">
+      <c r="A12" s="15">
         <v>45736.7642705787</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="13" t="s">
+      <c r="B12" s="16" t="s">
         <v>55</v>
       </c>
+      <c r="C12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" s="20">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7">
+      <c r="A13" s="10">
         <v>45736.95222440972</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>59</v>
-      </c>
+      <c r="B13" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="13"/>
+      <c r="H13" s="14"/>
     </row>
     <row r="14">
-      <c r="A14" s="10">
+      <c r="A14" s="15">
         <v>45736.99910443287</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>63</v>
+      <c r="B14" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="20">
+        <v>2.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15">
+      <c r="A15" s="10">
         <v>45737.32620246528</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>68</v>
+      <c r="B15" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="14"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15">
+        <v>45737.60551371527</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" s="8"/>
+      <c r="H16" s="9"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10">
+        <v>45738.71291584491</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15">
+        <v>45738.71346280092</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10">
+        <v>45738.7174087037</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21">
+        <v>45738.718439131946</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="108">
   <si>
     <t>Timestamp</t>
   </si>
@@ -309,6 +309,36 @@
   </si>
   <si>
     <t>0791352339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grace </t>
+  </si>
+  <si>
+    <t>Kimaru</t>
+  </si>
+  <si>
+    <t>Wanjiru</t>
+  </si>
+  <si>
+    <t>grace22kimaru@gmail.com</t>
+  </si>
+  <si>
+    <t>0746493578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremiah </t>
+  </si>
+  <si>
+    <t>Wanjohi</t>
+  </si>
+  <si>
+    <t>Kabiru</t>
+  </si>
+  <si>
+    <t>jerewanjohi346@gmail.com</t>
+  </si>
+  <si>
+    <t>0728446701</t>
   </si>
 </sst>
 </file>
@@ -630,7 +660,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H20" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H22" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -1258,23 +1288,63 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21">
+      <c r="A20" s="15">
         <v>45738.718439131946</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="F20" s="17" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10">
+        <v>45739.50798744213</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21">
+        <v>45739.51776155093</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="113">
   <si>
     <t>Timestamp</t>
   </si>
@@ -339,6 +339,21 @@
   </si>
   <si>
     <t>0728446701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rachael </t>
+  </si>
+  <si>
+    <t>Mwelu</t>
+  </si>
+  <si>
+    <t>Mutuku</t>
+  </si>
+  <si>
+    <t>rachaelmwelu79@gmail.com</t>
+  </si>
+  <si>
+    <t>0707615823</t>
   </si>
 </sst>
 </file>
@@ -502,10 +517,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -513,13 +528,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -660,7 +675,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H22" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H23" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -1328,23 +1343,43 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="21">
+      <c r="A22" s="15">
         <v>45739.51776155093</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="F22" s="23" t="s">
+      <c r="F22" s="17" t="s">
         <v>107</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21">
+        <v>45739.57386871528</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="122">
   <si>
     <t>Timestamp</t>
   </si>
@@ -354,6 +354,33 @@
   </si>
   <si>
     <t>0707615823</t>
+  </si>
+  <si>
+    <t>Miller</t>
+  </si>
+  <si>
+    <t>Adulu</t>
+  </si>
+  <si>
+    <t>milleradulu@gmail.com</t>
+  </si>
+  <si>
+    <t>0703175638</t>
+  </si>
+  <si>
+    <t>Leah</t>
+  </si>
+  <si>
+    <t>Muringi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muringo </t>
+  </si>
+  <si>
+    <t>lmmuringo@gmail.com</t>
+  </si>
+  <si>
+    <t>+254718891292</t>
   </si>
 </sst>
 </file>
@@ -544,7 +571,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -612,9 +639,6 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf quotePrefix="1" borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -675,7 +699,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H23" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H25" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -1363,23 +1387,60 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21">
+      <c r="A23" s="10">
         <v>45739.57386871528</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="F23" s="23" t="s">
+      <c r="F23" s="12" t="s">
         <v>112</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15">
+        <v>45739.59026469907</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21">
+        <v>45739.60710328704</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="128">
   <si>
     <t>Timestamp</t>
   </si>
@@ -341,6 +341,9 @@
     <t>0728446701</t>
   </si>
   <si>
+    <t>Managed to test out the course flow and confirmed all works well there. Once a member logs out, they have to close the to remove the stagnant screen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rachael </t>
   </si>
   <si>
@@ -356,6 +359,9 @@
     <t>0707615823</t>
   </si>
   <si>
+    <t>Tested out the app and confirmed most of the features are working</t>
+  </si>
+  <si>
     <t>Miller</t>
   </si>
   <si>
@@ -381,6 +387,18 @@
   </si>
   <si>
     <t>+254718891292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wanjohi </t>
+  </si>
+  <si>
+    <t>Brianwanjohi80@gmail.com</t>
+  </si>
+  <si>
+    <t>0759932474</t>
   </si>
 </sst>
 </file>
@@ -544,10 +562,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -555,13 +573,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -571,7 +589,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="33">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -627,18 +645,48 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="10" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf quotePrefix="1" borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -699,7 +747,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H25" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H26" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -915,7 +963,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="14" width="18.88"/>
+    <col customWidth="1" min="1" max="6" width="18.88"/>
+    <col customWidth="1" min="7" max="7" width="37.75"/>
+    <col customWidth="1" min="8" max="14" width="18.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1175,10 +1225,10 @@
       <c r="F12" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="21">
         <v>3.0</v>
       </c>
     </row>
@@ -1198,7 +1248,7 @@
       <c r="F13" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="13"/>
+      <c r="G13" s="22"/>
       <c r="H13" s="14"/>
     </row>
     <row r="14">
@@ -1218,10 +1268,10 @@
       <c r="F14" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="21">
         <v>2.0</v>
       </c>
     </row>
@@ -1244,7 +1294,7 @@
       <c r="F15" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="G15" s="13"/>
+      <c r="G15" s="22"/>
       <c r="H15" s="14"/>
     </row>
     <row r="16">
@@ -1266,7 +1316,7 @@
       <c r="F16" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="G16" s="8"/>
+      <c r="G16" s="23"/>
       <c r="H16" s="9"/>
     </row>
     <row r="17">
@@ -1288,6 +1338,7 @@
       <c r="F17" s="12" t="s">
         <v>83</v>
       </c>
+      <c r="G17" s="24"/>
     </row>
     <row r="18">
       <c r="A18" s="15">
@@ -1305,6 +1356,7 @@
       <c r="F18" s="17" t="s">
         <v>87</v>
       </c>
+      <c r="G18" s="25"/>
     </row>
     <row r="19">
       <c r="A19" s="10">
@@ -1325,6 +1377,7 @@
       <c r="F19" s="12" t="s">
         <v>92</v>
       </c>
+      <c r="G19" s="24"/>
     </row>
     <row r="20">
       <c r="A20" s="15">
@@ -1345,6 +1398,7 @@
       <c r="F20" s="17" t="s">
         <v>97</v>
       </c>
+      <c r="G20" s="25"/>
     </row>
     <row r="21">
       <c r="A21" s="10">
@@ -1365,6 +1419,7 @@
       <c r="F21" s="12" t="s">
         <v>102</v>
       </c>
+      <c r="G21" s="24"/>
     </row>
     <row r="22">
       <c r="A22" s="15">
@@ -1385,25 +1440,37 @@
       <c r="F22" s="17" t="s">
         <v>107</v>
       </c>
+      <c r="G22" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="H22" s="27">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="10">
         <v>45739.57386871528</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="H23" s="29">
+        <v>4.0</v>
       </c>
     </row>
     <row r="24">
@@ -1411,36 +1478,53 @@
         <v>45739.59026469907</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21">
+      <c r="A25" s="10">
         <v>45739.60710328704</v>
       </c>
-      <c r="B25" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="C25" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="D25" s="22" t="s">
+      <c r="B25" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="E25" s="22" t="s">
+      <c r="C25" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="F25" s="22" t="s">
+      <c r="D25" s="11" t="s">
         <v>121</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="30">
+        <v>45742.417584131945</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="133">
   <si>
     <t>Timestamp</t>
   </si>
@@ -119,6 +119,14 @@
   </si>
   <si>
     <t>+254720107685</t>
+  </si>
+  <si>
+    <t>Here's some feedback regarding The PRF App.
+1.⁠ ⁠Really great work and input..
+2.⁠ ⁠One the default home space, one cannot exit unless they minimise... maybe introduce something where if one presses the 'back button" twice, they are able to exit. 
+3.⁠ ⁠The app is user friendly.
+4.⁠ ⁠Do we have a web version of the same or just the mobile version? Can I use it on my laptop for example?
+5.⁠ ⁠Zingine zikikuja nitasema</t>
   </si>
   <si>
     <t xml:space="preserve">Eugene </t>
@@ -399,6 +407,18 @@
   </si>
   <si>
     <t>0759932474</t>
+  </si>
+  <si>
+    <t>Franklin</t>
+  </si>
+  <si>
+    <t>Kamunde</t>
+  </si>
+  <si>
+    <t>kamunde1@gmail.com</t>
+  </si>
+  <si>
+    <t>0725207549</t>
   </si>
 </sst>
 </file>
@@ -562,10 +582,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -573,13 +593,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -589,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -645,10 +665,13 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -747,7 +770,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H26" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H27" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -1117,27 +1140,31 @@
       <c r="F7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="14"/>
+      <c r="G7" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="19">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="15">
         <v>45729.98487356481</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>19</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="9"/>
@@ -1147,19 +1174,19 @@
         <v>45736.66063238426</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="14"/>
@@ -1169,19 +1196,19 @@
         <v>45736.72968936343</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="9"/>
@@ -1191,19 +1218,19 @@
         <v>45736.73206912037</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11" s="18" t="s">
         <v>54</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>55</v>
       </c>
       <c r="H11" s="19">
         <v>1.0</v>
@@ -1214,21 +1241,21 @@
         <v>45736.7642705787</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="21">
+      <c r="G12" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="22">
         <v>3.0</v>
       </c>
     </row>
@@ -1237,18 +1264,18 @@
         <v>45736.95222440972</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="22"/>
+        <v>64</v>
+      </c>
+      <c r="G13" s="23"/>
       <c r="H13" s="14"/>
     </row>
     <row r="14">
@@ -1256,22 +1283,22 @@
         <v>45736.99910443287</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="21">
+      <c r="G14" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14" s="22">
         <v>2.0</v>
       </c>
     </row>
@@ -1280,21 +1307,21 @@
         <v>45737.32620246528</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" s="22"/>
+        <v>74</v>
+      </c>
+      <c r="G15" s="23"/>
       <c r="H15" s="14"/>
     </row>
     <row r="16">
@@ -1302,21 +1329,21 @@
         <v>45737.60551371527</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" s="23"/>
+        <v>79</v>
+      </c>
+      <c r="G16" s="24"/>
       <c r="H16" s="9"/>
     </row>
     <row r="17">
@@ -1324,126 +1351,126 @@
         <v>45738.71291584491</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G17" s="24"/>
+        <v>84</v>
+      </c>
+      <c r="G17" s="25"/>
     </row>
     <row r="18">
       <c r="A18" s="15">
         <v>45738.71346280092</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="G18" s="25"/>
+        <v>88</v>
+      </c>
+      <c r="G18" s="26"/>
     </row>
     <row r="19">
       <c r="A19" s="10">
         <v>45738.7174087037</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="G19" s="24"/>
+        <v>93</v>
+      </c>
+      <c r="G19" s="25"/>
     </row>
     <row r="20">
       <c r="A20" s="15">
         <v>45738.718439131946</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G20" s="25"/>
+        <v>98</v>
+      </c>
+      <c r="G20" s="26"/>
     </row>
     <row r="21">
       <c r="A21" s="10">
         <v>45739.50798744213</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="G21" s="24"/>
+        <v>103</v>
+      </c>
+      <c r="G21" s="25"/>
     </row>
     <row r="22">
       <c r="A22" s="15">
         <v>45739.51776155093</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="G22" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="H22" s="27">
+      <c r="G22" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="H22" s="28">
         <v>5.0</v>
       </c>
     </row>
@@ -1452,24 +1479,24 @@
         <v>45739.57386871528</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="G23" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="H23" s="29">
+      <c r="G23" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="H23" s="30">
         <v>4.0</v>
       </c>
     </row>
@@ -1478,16 +1505,16 @@
         <v>45739.59026469907</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25">
@@ -1495,36 +1522,53 @@
         <v>45739.60710328704</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="30">
+      <c r="A26" s="15">
         <v>45742.417584131945</v>
       </c>
-      <c r="B26" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C26" s="31" t="s">
+      <c r="B26" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="E26" s="31" t="s">
+      <c r="C26" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="F26" s="32" t="s">
+      <c r="E26" s="16" t="s">
         <v>127</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31">
+        <v>45742.64363893519</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="138">
   <si>
     <t>Timestamp</t>
   </si>
@@ -419,6 +419,21 @@
   </si>
   <si>
     <t>0725207549</t>
+  </si>
+  <si>
+    <t>Abel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mutiso </t>
+  </si>
+  <si>
+    <t>Manoti</t>
+  </si>
+  <si>
+    <t>mutisoabel@gmail.com</t>
+  </si>
+  <si>
+    <t>0728711637</t>
   </si>
 </sst>
 </file>
@@ -582,10 +597,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -593,13 +608,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -770,7 +785,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H27" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H28" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -1555,20 +1570,40 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="31">
+      <c r="A27" s="10">
         <v>45742.64363893519</v>
       </c>
-      <c r="B27" s="32" t="s">
+      <c r="B27" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C27" s="32" t="s">
+      <c r="C27" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E27" s="32" t="s">
+      <c r="E27" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F27" s="33" t="s">
+      <c r="F27" s="12" t="s">
         <v>132</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31">
+        <v>45742.89663130787</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="E28" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="F28" s="33" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adulu/Work/PRF/SuperApp/API/prf/app/Console/Commands/Member/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56310F7-9130-1149-A817-A8187C4E6091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="4440" yWindow="760" windowWidth="25800" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Form Responses 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="143">
   <si>
     <t>Timestamp</t>
   </si>
@@ -435,22 +444,38 @@
   <si>
     <t>0728711637</t>
   </si>
+  <si>
+    <t xml:space="preserve">Nicholas Muhoya </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ngatia </t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>muhoyanick@gmail.com</t>
+  </si>
+  <si>
+    <t>0711858647</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -461,11 +486,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="12">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF442F65"/>
@@ -479,6 +510,7 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -493,6 +525,7 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -507,6 +540,7 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -521,6 +555,7 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -535,6 +570,7 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -549,6 +585,7 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -563,6 +600,7 @@
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -577,6 +615,7 @@
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -591,6 +630,7 @@
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -605,6 +645,7 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -619,189 +660,128 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf quotePrefix="1" borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf quotePrefix="1" borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf quotePrefix="1" borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf quotePrefix="1" borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="3">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="3" pivot="0" name="Form Responses 1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Form Responses 1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H28" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses1" displayName="Form_Responses1" ref="A1:H30">
   <tableColumns count="8">
-    <tableColumn name="Timestamp" id="1"/>
-    <tableColumn name="First Name" id="2"/>
-    <tableColumn name="Last Name" id="3"/>
-    <tableColumn name="Other Names" id="4"/>
-    <tableColumn name="Email Address" id="5"/>
-    <tableColumn name="Phone Number" id="6"/>
-    <tableColumn name="Feedback" id="7"/>
-    <tableColumn name="Feedback Order" id="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Timestamp"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="First Name"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Last Name"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Other Names"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Email Address"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Phone Number"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Feedback"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Feedback Order"/>
   </tableColumns>
-  <tableStyleInfo name="Form Responses 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Form Responses 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -991,22 +971,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="18.88"/>
-    <col customWidth="1" min="7" max="7" width="37.75"/>
-    <col customWidth="1" min="8" max="14" width="18.88"/>
+    <col min="1" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="37.6640625" customWidth="1"/>
+    <col min="8" max="14" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1025,591 +1008,618 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="4">
         <v>45728.821473171294</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="9"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="10">
+      <c r="G2" s="5"/>
+      <c r="H2" s="7"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="8">
         <v>45729.213411793986</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="14"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="15">
-        <v>45729.26696155092</v>
-      </c>
-      <c r="B4" s="16" t="s">
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="4">
+        <v>45729.266961550922</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="9"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10">
-        <v>45729.32677667824</v>
-      </c>
-      <c r="B5" s="11" t="s">
+      <c r="G4" s="5"/>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="8">
+        <v>45729.326776678237</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="15">
-        <v>45729.53855537037</v>
-      </c>
-      <c r="B6" s="16" t="s">
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="4">
+        <v>45729.538555370367</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="9"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="10">
-        <v>45729.54199271991</v>
-      </c>
-      <c r="B7" s="11" t="s">
+      <c r="G6" s="5"/>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="8">
+        <v>45729.541992719911</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="19">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15">
-        <v>45729.98487356481</v>
-      </c>
-      <c r="B8" s="16" t="s">
+      <c r="H7" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="4">
+        <v>45729.984873564812</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="9"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10">
-        <v>45736.66063238426</v>
-      </c>
-      <c r="B9" s="11" t="s">
+      <c r="G8" s="5"/>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="8">
+        <v>45736.660632384257</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="14"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="15">
-        <v>45736.72968936343</v>
-      </c>
-      <c r="B10" s="16" t="s">
+      <c r="G9" s="9"/>
+      <c r="H9" s="11"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="4">
+        <v>45736.729689363427</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10">
-        <v>45736.73206912037</v>
-      </c>
-      <c r="B11" s="11" t="s">
+      <c r="G10" s="5"/>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="8">
+        <v>45736.732069120371</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="19">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15">
+      <c r="H11" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="4">
         <v>45736.7642705787</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="H12" s="22">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10">
-        <v>45736.95222440972</v>
-      </c>
-      <c r="B13" s="11" t="s">
+      <c r="H12" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="8">
+        <v>45736.952224409717</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="14"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="15">
-        <v>45736.99910443287</v>
-      </c>
-      <c r="B14" s="16" t="s">
+      <c r="G13" s="12"/>
+      <c r="H13" s="11"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="4">
+        <v>45736.999104432871</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16" t="s">
+      <c r="D14" s="5"/>
+      <c r="E14" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="21" t="s">
+      <c r="G14" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="H14" s="22">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10">
-        <v>45737.32620246528</v>
-      </c>
-      <c r="B15" s="11" t="s">
+      <c r="H14" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="8">
+        <v>45737.326202465279</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="14"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15">
-        <v>45737.60551371527</v>
-      </c>
-      <c r="B16" s="16" t="s">
+      <c r="G15" s="12"/>
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="4">
+        <v>45737.605513715273</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="24"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="10">
+      <c r="G16" s="13"/>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="8">
         <v>45738.71291584491</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G17" s="25"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15">
-        <v>45738.71346280092</v>
-      </c>
-      <c r="B18" s="16" t="s">
+      <c r="G17" s="12"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="4">
+        <v>45738.713462800923</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="G18" s="26"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="10">
-        <v>45738.7174087037</v>
-      </c>
-      <c r="B19" s="11" t="s">
+      <c r="G18" s="13"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="8">
+        <v>45738.717408703698</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="G19" s="25"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="15">
+      <c r="G19" s="12"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="4">
         <v>45738.718439131946</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="G20" s="26"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="10">
-        <v>45739.50798744213</v>
-      </c>
-      <c r="B21" s="11" t="s">
+      <c r="G20" s="13"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="8">
+        <v>45739.507987442128</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="G21" s="25"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15">
-        <v>45739.51776155093</v>
-      </c>
-      <c r="B22" s="16" t="s">
+      <c r="G21" s="12"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="4">
+        <v>45739.517761550931</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="G22" s="27" t="s">
+      <c r="G22" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H22" s="28">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10">
-        <v>45739.57386871528</v>
-      </c>
-      <c r="B23" s="11" t="s">
+      <c r="H22" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="8">
+        <v>45739.573868715277</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="29" t="s">
+      <c r="G23" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="H23" s="30">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15">
-        <v>45739.59026469907</v>
-      </c>
-      <c r="B24" s="16" t="s">
+      <c r="H23" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="4">
+        <v>45739.590264699073</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10">
-        <v>45739.60710328704</v>
-      </c>
-      <c r="B25" s="11" t="s">
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="8">
+        <v>45739.607103287039</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="9" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="15">
+    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="4">
         <v>45742.417584131945</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="F26" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="10">
-        <v>45742.64363893519</v>
-      </c>
-      <c r="B27" s="11" t="s">
+    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="8">
+        <v>45742.643638935187</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="F27" s="10" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="31">
-        <v>45742.89663130787</v>
-      </c>
-      <c r="B28" s="32" t="s">
+    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="4">
+        <v>45742.896631307871</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C28" s="32" t="s">
+      <c r="C28" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E28" s="32" t="s">
+      <c r="E28" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F28" s="33" t="s">
+      <c r="F28" s="6" t="s">
         <v>137</v>
       </c>
     </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="8">
+        <v>45743.999212106486</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="14"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="16"/>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -1,26 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adulu/Work/PRF/SuperApp/API/prf/app/Console/Commands/Member/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56310F7-9130-1149-A817-A8187C4E6091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="4440" yWindow="760" windowWidth="25800" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Form Responses 1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="151">
   <si>
     <t>Timestamp</t>
   </si>
@@ -459,23 +450,46 @@
   <si>
     <t>0711858647</t>
   </si>
+  <si>
+    <t xml:space="preserve">Mwangi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maina </t>
+  </si>
+  <si>
+    <t>mwangi.maina16@gmail.com</t>
+  </si>
+  <si>
+    <t>0722610870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VELLOUR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NASAMBU </t>
+  </si>
+  <si>
+    <t>vellourzawady@gmail.com</t>
+  </si>
+  <si>
+    <t>0115999143</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -486,17 +500,11 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="12">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF442F65"/>
@@ -510,7 +518,6 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -525,7 +532,6 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -540,7 +546,6 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -555,7 +560,6 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -570,7 +574,6 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -585,7 +588,6 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -600,7 +602,6 @@
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -615,7 +616,6 @@
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -630,158 +630,217 @@
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+  <cellXfs count="34">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf quotePrefix="1" borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf quotePrefix="1" borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf quotePrefix="1" borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf quotePrefix="1" borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5B3F86"/>
+          <bgColor rgb="FF5B3F86"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8F9FA"/>
           <bgColor rgb="FFF8F9FA"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF5B3F86"/>
-          <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
+      <border/>
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="Form Responses 1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+    <tableStyle count="3" pivot="0" name="Form Responses 1-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses1" displayName="Form_Responses1" ref="A1:H30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H31" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Timestamp"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="First Name"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Last Name"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Other Names"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Email Address"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Phone Number"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Feedback"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Feedback Order"/>
+    <tableColumn name="Timestamp" id="1"/>
+    <tableColumn name="First Name" id="2"/>
+    <tableColumn name="Last Name" id="3"/>
+    <tableColumn name="Other Names" id="4"/>
+    <tableColumn name="Email Address" id="5"/>
+    <tableColumn name="Phone Number" id="6"/>
+    <tableColumn name="Feedback" id="7"/>
+    <tableColumn name="Feedback Order" id="8"/>
   </tableColumns>
-  <tableStyleInfo name="Form Responses 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="Form Responses 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -971,25 +1030,22 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="37.6640625" customWidth="1"/>
-    <col min="8" max="14" width="18.83203125" customWidth="1"/>
+    <col customWidth="1" min="1" max="6" width="18.88"/>
+    <col customWidth="1" min="7" max="7" width="37.75"/>
+    <col customWidth="1" min="8" max="14" width="18.88"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1008,618 +1064,646 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="4">
+    <row r="2">
+      <c r="A2" s="5">
         <v>45728.821473171294</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="8">
+      <c r="G2" s="8"/>
+      <c r="H2" s="9"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="10">
         <v>45729.213411793986</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="11"/>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="4">
-        <v>45729.266961550922</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="G3" s="13"/>
+      <c r="H3" s="14"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="15">
+        <v>45729.26696155092</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="8">
-        <v>45729.326776678237</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="G4" s="8"/>
+      <c r="H4" s="9"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10">
+        <v>45729.32677667824</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="11"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="4">
-        <v>45729.538555370367</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="G5" s="13"/>
+      <c r="H5" s="14"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="15">
+        <v>45729.53855537037</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="8">
-        <v>45729.541992719911</v>
-      </c>
-      <c r="B7" s="9" t="s">
+      <c r="G6" s="8"/>
+      <c r="H6" s="9"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10">
+        <v>45729.54199271991</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="4">
-        <v>45729.984873564812</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="H7" s="19">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15">
+        <v>45729.98487356481</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="8">
-        <v>45736.660632384257</v>
-      </c>
-      <c r="B9" s="9" t="s">
+      <c r="G8" s="8"/>
+      <c r="H8" s="9"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10">
+        <v>45736.66063238426</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="11"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="4">
-        <v>45736.729689363427</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="G9" s="13"/>
+      <c r="H9" s="14"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15">
+        <v>45736.72968936343</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="8">
-        <v>45736.732069120371</v>
-      </c>
-      <c r="B11" s="9" t="s">
+      <c r="G10" s="8"/>
+      <c r="H10" s="9"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10">
+        <v>45736.73206912037</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="4">
+      <c r="H11" s="19">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15">
         <v>45736.7642705787</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="H12" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="8">
-        <v>45736.952224409717</v>
-      </c>
-      <c r="B13" s="9" t="s">
+      <c r="H12" s="22">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10">
+        <v>45736.95222440972</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="11"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="4">
-        <v>45736.999104432871</v>
-      </c>
-      <c r="B14" s="5" t="s">
+      <c r="G13" s="23"/>
+      <c r="H13" s="14"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15">
+        <v>45736.99910443287</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5" t="s">
+      <c r="D14" s="16"/>
+      <c r="E14" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="H14" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="8">
-        <v>45737.326202465279</v>
-      </c>
-      <c r="B15" s="9" t="s">
+      <c r="H14" s="22">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10">
+        <v>45737.32620246528</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="G15" s="12"/>
-      <c r="H15" s="11"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="4">
-        <v>45737.605513715273</v>
-      </c>
-      <c r="B16" s="5" t="s">
+      <c r="G15" s="23"/>
+      <c r="H15" s="14"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15">
+        <v>45737.60551371527</v>
+      </c>
+      <c r="B16" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="8">
+      <c r="G16" s="24"/>
+      <c r="H16" s="9"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10">
         <v>45738.71291584491</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="G17" s="12"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="4">
-        <v>45738.713462800923</v>
-      </c>
-      <c r="B18" s="5" t="s">
+      <c r="G17" s="25"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15">
+        <v>45738.71346280092</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="G18" s="13"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="8">
-        <v>45738.717408703698</v>
-      </c>
-      <c r="B19" s="9" t="s">
+      <c r="G18" s="26"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10">
+        <v>45738.7174087037</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="G19" s="12"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="4">
+      <c r="G19" s="25"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15">
         <v>45738.718439131946</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="G20" s="13"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="8">
-        <v>45739.507987442128</v>
-      </c>
-      <c r="B21" s="9" t="s">
+      <c r="G20" s="26"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10">
+        <v>45739.50798744213</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="G21" s="12"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="4">
-        <v>45739.517761550931</v>
-      </c>
-      <c r="B22" s="5" t="s">
+      <c r="G21" s="25"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15">
+        <v>45739.51776155093</v>
+      </c>
+      <c r="B22" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="G22" s="13" t="s">
+      <c r="G22" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="H22" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="8">
-        <v>45739.573868715277</v>
-      </c>
-      <c r="B23" s="9" t="s">
+      <c r="H22" s="28">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10">
+        <v>45739.57386871528</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="H23" s="11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="4">
-        <v>45739.590264699073</v>
-      </c>
-      <c r="B24" s="5" t="s">
+      <c r="H23" s="30">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15">
+        <v>45739.59026469907</v>
+      </c>
+      <c r="B24" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="17" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="8">
-        <v>45739.607103287039</v>
-      </c>
-      <c r="B25" s="9" t="s">
+    <row r="25">
+      <c r="A25" s="10">
+        <v>45739.60710328704</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="4">
+    <row r="26">
+      <c r="A26" s="15">
         <v>45742.417584131945</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="17" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="8">
-        <v>45742.643638935187</v>
-      </c>
-      <c r="B27" s="9" t="s">
+    <row r="27">
+      <c r="A27" s="10">
+        <v>45742.64363893519</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="12" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="4">
-        <v>45742.896631307871</v>
-      </c>
-      <c r="B28" s="5" t="s">
+    <row r="28">
+      <c r="A28" s="15">
+        <v>45742.89663130787</v>
+      </c>
+      <c r="B28" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="17" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="8">
+    <row r="29">
+      <c r="A29" s="10">
         <v>45743.999212106486</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="12" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="14"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="16"/>
+    <row r="30">
+      <c r="A30" s="15">
+        <v>45745.549431770836</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="31">
+        <v>45747.62957160879</v>
+      </c>
+      <c r="B31" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="F31" s="33" t="s">
+        <v>150</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="166">
   <si>
     <t>Timestamp</t>
   </si>
@@ -473,6 +473,51 @@
   </si>
   <si>
     <t>0115999143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juliet </t>
+  </si>
+  <si>
+    <t>Eboya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esingiri </t>
+  </si>
+  <si>
+    <t>julieteboya98@gmail.com</t>
+  </si>
+  <si>
+    <t>0745632548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regina </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Njeri </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muturi </t>
+  </si>
+  <si>
+    <t>reginahnjeri01@gmail.com</t>
+  </si>
+  <si>
+    <t>0737935052</t>
+  </si>
+  <si>
+    <t>Eugene</t>
+  </si>
+  <si>
+    <t>Mukadi</t>
+  </si>
+  <si>
+    <t>Wilbur</t>
+  </si>
+  <si>
+    <t>euwiimukadi@gmail.com</t>
+  </si>
+  <si>
+    <t>0702012447</t>
   </si>
 </sst>
 </file>
@@ -636,10 +681,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -647,13 +692,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -824,7 +869,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H31" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H34" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -1683,21 +1728,81 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="31">
+      <c r="A31" s="10">
         <v>45747.62957160879</v>
       </c>
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="C31" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32" t="s">
+      <c r="D31" s="11"/>
+      <c r="E31" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="F31" s="33" t="s">
+      <c r="F31" s="12" t="s">
         <v>150</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15">
+        <v>45755.83148662037</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10">
+        <v>45755.83326489583</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="31">
+        <v>45755.8337792824</v>
+      </c>
+      <c r="B34" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="C34" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="D34" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="E34" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="F34" s="33" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="180">
   <si>
     <t>Timestamp</t>
   </si>
@@ -518,6 +518,48 @@
   </si>
   <si>
     <t>0702012447</t>
+  </si>
+  <si>
+    <t>Grace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wanjiru </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graciey </t>
+  </si>
+  <si>
+    <t>gracieyhr@gmail.com</t>
+  </si>
+  <si>
+    <t>+254769960734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joseph </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muli </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muthoki </t>
+  </si>
+  <si>
+    <t>mulijoseph052@gmail.com</t>
+  </si>
+  <si>
+    <t>0794649517</t>
+  </si>
+  <si>
+    <t>Felix</t>
+  </si>
+  <si>
+    <t>Mungai</t>
+  </si>
+  <si>
+    <t>mungaifelix@gmail.com</t>
+  </si>
+  <si>
+    <t>+254721138067</t>
   </si>
 </sst>
 </file>
@@ -681,10 +723,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -692,13 +734,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -708,7 +750,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -806,9 +848,6 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf quotePrefix="1" borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -869,7 +908,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H34" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H37" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -1786,23 +1825,80 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="31">
+      <c r="A34" s="15">
         <v>45755.8337792824</v>
       </c>
-      <c r="B34" s="32" t="s">
+      <c r="B34" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="C34" s="32" t="s">
+      <c r="C34" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="E34" s="32" t="s">
+      <c r="E34" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="F34" s="33" t="s">
+      <c r="F34" s="17" t="s">
         <v>165</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10">
+        <v>45762.83953494213</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15">
+        <v>45763.48679163195</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="31">
+        <v>45774.85872887731</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="C37" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="E37" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="F37" s="32" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adulu/Work/PRF/SuperApp/API/prf/app/Console/Commands/Member/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1811281-C118-9642-996A-27BD1D3EB0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="4440" yWindow="760" windowWidth="25800" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Form Responses 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -526,9 +535,6 @@
     <t xml:space="preserve">Wanjiru </t>
   </si>
   <si>
-    <t xml:space="preserve">Graciey </t>
-  </si>
-  <si>
     <t>gracieyhr@gmail.com</t>
   </si>
   <si>
@@ -560,25 +566,36 @@
   </si>
   <si>
     <t>+254721138067</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -587,11 +604,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="12">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF442F65"/>
@@ -605,6 +628,7 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -619,6 +643,7 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -633,6 +658,7 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -647,6 +673,7 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -661,6 +688,7 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -675,6 +703,7 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -689,6 +718,7 @@
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -703,6 +733,7 @@
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -717,6 +748,7 @@
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -731,6 +763,7 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -745,186 +778,128 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf quotePrefix="1" borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf quotePrefix="1" borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf quotePrefix="1" borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="3">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="3" pivot="0" name="Form Responses 1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Form Responses 1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H37" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses1" displayName="Form_Responses1" ref="A1:H37">
   <tableColumns count="8">
-    <tableColumn name="Timestamp" id="1"/>
-    <tableColumn name="First Name" id="2"/>
-    <tableColumn name="Last Name" id="3"/>
-    <tableColumn name="Other Names" id="4"/>
-    <tableColumn name="Email Address" id="5"/>
-    <tableColumn name="Phone Number" id="6"/>
-    <tableColumn name="Feedback" id="7"/>
-    <tableColumn name="Feedback Order" id="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Timestamp"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="First Name"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Last Name"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Other Names"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Email Address"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Phone Number"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Feedback"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Feedback Order"/>
   </tableColumns>
-  <tableStyleInfo name="Form Responses 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Form Responses 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1114,22 +1089,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="18.88"/>
-    <col customWidth="1" min="7" max="7" width="37.75"/>
-    <col customWidth="1" min="8" max="14" width="18.88"/>
+    <col min="1" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="37.6640625" customWidth="1"/>
+    <col min="8" max="14" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1148,763 +1126,763 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="4">
         <v>45728.821473171294</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="9"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="10">
+      <c r="G2" s="5"/>
+      <c r="H2" s="7"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="8">
         <v>45729.213411793986</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="14"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="15">
-        <v>45729.26696155092</v>
-      </c>
-      <c r="B4" s="16" t="s">
+      <c r="G3" s="9"/>
+      <c r="H3" s="11"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="4">
+        <v>45729.266961550922</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="9"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10">
-        <v>45729.32677667824</v>
-      </c>
-      <c r="B5" s="11" t="s">
+      <c r="G4" s="5"/>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="8">
+        <v>45729.326776678237</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="15">
-        <v>45729.53855537037</v>
-      </c>
-      <c r="B6" s="16" t="s">
+      <c r="G5" s="9"/>
+      <c r="H5" s="11"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="4">
+        <v>45729.538555370367</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="9"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="10">
-        <v>45729.54199271991</v>
-      </c>
-      <c r="B7" s="11" t="s">
+      <c r="G6" s="5"/>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="8">
+        <v>45729.541992719911</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="19">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15">
-        <v>45729.98487356481</v>
-      </c>
-      <c r="B8" s="16" t="s">
+      <c r="H7" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="4">
+        <v>45729.984873564812</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="9"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10">
-        <v>45736.66063238426</v>
-      </c>
-      <c r="B9" s="11" t="s">
+      <c r="G8" s="5"/>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="8">
+        <v>45736.660632384257</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="14"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="15">
-        <v>45736.72968936343</v>
-      </c>
-      <c r="B10" s="16" t="s">
+      <c r="G9" s="9"/>
+      <c r="H9" s="11"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="4">
+        <v>45736.729689363427</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10">
-        <v>45736.73206912037</v>
-      </c>
-      <c r="B11" s="11" t="s">
+      <c r="G10" s="5"/>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="8">
+        <v>45736.732069120371</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="19">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15">
+      <c r="H11" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="4">
         <v>45736.7642705787</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="H12" s="22">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10">
-        <v>45736.95222440972</v>
-      </c>
-      <c r="B13" s="11" t="s">
+      <c r="H12" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="8">
+        <v>45736.952224409717</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="14"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="15">
-        <v>45736.99910443287</v>
-      </c>
-      <c r="B14" s="16" t="s">
+      <c r="G13" s="12"/>
+      <c r="H13" s="11"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="4">
+        <v>45736.999104432871</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16" t="s">
+      <c r="D14" s="5"/>
+      <c r="E14" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="21" t="s">
+      <c r="G14" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="H14" s="22">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10">
-        <v>45737.32620246528</v>
-      </c>
-      <c r="B15" s="11" t="s">
+      <c r="H14" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="8">
+        <v>45737.326202465279</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="14"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15">
-        <v>45737.60551371527</v>
-      </c>
-      <c r="B16" s="16" t="s">
+      <c r="G15" s="12"/>
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="4">
+        <v>45737.605513715273</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="24"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="10">
+      <c r="G16" s="13"/>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="8">
         <v>45738.71291584491</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G17" s="25"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15">
-        <v>45738.71346280092</v>
-      </c>
-      <c r="B18" s="16" t="s">
+      <c r="G17" s="12"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="4">
+        <v>45738.713462800923</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="G18" s="26"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="10">
-        <v>45738.7174087037</v>
-      </c>
-      <c r="B19" s="11" t="s">
+      <c r="G18" s="13"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="8">
+        <v>45738.717408703698</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="G19" s="25"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="15">
+      <c r="G19" s="12"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="4">
         <v>45738.718439131946</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="G20" s="26"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="10">
-        <v>45739.50798744213</v>
-      </c>
-      <c r="B21" s="11" t="s">
+      <c r="G20" s="13"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="8">
+        <v>45739.507987442128</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="G21" s="25"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15">
-        <v>45739.51776155093</v>
-      </c>
-      <c r="B22" s="16" t="s">
+      <c r="G21" s="12"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="4">
+        <v>45739.517761550931</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="G22" s="27" t="s">
+      <c r="G22" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H22" s="28">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10">
-        <v>45739.57386871528</v>
-      </c>
-      <c r="B23" s="11" t="s">
+      <c r="H22" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="8">
+        <v>45739.573868715277</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="29" t="s">
+      <c r="G23" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="H23" s="30">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15">
-        <v>45739.59026469907</v>
-      </c>
-      <c r="B24" s="16" t="s">
+      <c r="H23" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="4">
+        <v>45739.590264699073</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10">
-        <v>45739.60710328704</v>
-      </c>
-      <c r="B25" s="11" t="s">
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="8">
+        <v>45739.607103287039</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="9" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="15">
+    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="4">
         <v>45742.417584131945</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="F26" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="10">
-        <v>45742.64363893519</v>
-      </c>
-      <c r="B27" s="11" t="s">
+    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="8">
+        <v>45742.643638935187</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="F27" s="10" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="15">
-        <v>45742.89663130787</v>
-      </c>
-      <c r="B28" s="16" t="s">
+    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="4">
+        <v>45742.896631307871</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="6" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10">
+    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="8">
         <v>45743.999212106486</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="F29" s="12" t="s">
+      <c r="F29" s="10" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="15">
+    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="4">
         <v>45745.549431770836</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="F30" s="17" t="s">
+      <c r="F30" s="6" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="10">
-        <v>45747.62957160879</v>
-      </c>
-      <c r="B31" s="11" t="s">
+    <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="8">
+        <v>45747.629571608792</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11" t="s">
+      <c r="D31" s="9"/>
+      <c r="E31" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="F31" s="12" t="s">
+      <c r="F31" s="10" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="15">
-        <v>45755.83148662037</v>
-      </c>
-      <c r="B32" s="16" t="s">
+    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="4">
+        <v>45755.831486620373</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="6" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="10">
-        <v>45755.83326489583</v>
-      </c>
-      <c r="B33" s="11" t="s">
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="8">
+        <v>45755.833264895831</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="F33" s="10" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="15">
-        <v>45755.8337792824</v>
-      </c>
-      <c r="B34" s="16" t="s">
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="4">
+        <v>45755.833779282402</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="E34" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="F34" s="6" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="10">
-        <v>45762.83953494213</v>
-      </c>
-      <c r="B35" s="11" t="s">
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="8">
+        <v>45762.839534942133</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="F35" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="F35" s="11" t="s">
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="4">
+        <v>45763.486791631949</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="15">
-        <v>45763.48679163195</v>
-      </c>
-      <c r="B36" s="16" t="s">
+      <c r="C36" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="D36" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="E36" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="E36" s="16" t="s">
+      <c r="F36" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="F36" s="17" t="s">
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="14">
+        <v>45774.858728877312</v>
+      </c>
+      <c r="B37" s="15" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="31">
-        <v>45774.85872887731</v>
-      </c>
-      <c r="B37" s="32" t="s">
+      <c r="C37" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C37" s="32" t="s">
+      <c r="E37" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="E37" s="32" t="s">
+      <c r="F37" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="F37" s="32" t="s">
-        <v>179</v>
-      </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -1,26 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adulu/Work/PRF/SuperApp/API/prf/app/Console/Commands/Member/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1811281-C118-9642-996A-27BD1D3EB0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="4440" yWindow="760" windowWidth="25800" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Form Responses 1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="184">
   <si>
     <t>Timestamp</t>
   </si>
@@ -535,6 +526,9 @@
     <t xml:space="preserve">Wanjiru </t>
   </si>
   <si>
+    <t xml:space="preserve">Graciey </t>
+  </si>
+  <si>
     <t>gracieyhr@gmail.com</t>
   </si>
   <si>
@@ -568,34 +562,35 @@
     <t>+254721138067</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>Cliff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gitonga </t>
+  </si>
+  <si>
+    <t>gitongaec@gmail.com</t>
+  </si>
+  <si>
+    <t>0710985400</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -604,17 +599,11 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="12">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF442F65"/>
@@ -628,7 +617,6 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -643,7 +631,6 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -658,7 +645,6 @@
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -673,7 +659,6 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -688,7 +673,6 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -703,7 +687,6 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -718,7 +701,6 @@
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -733,7 +715,6 @@
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -748,158 +729,217 @@
       <bottom style="thin">
         <color rgb="FFF8F9FA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+  <cellXfs count="34">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf quotePrefix="1" borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf quotePrefix="1" borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf quotePrefix="1" borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf quotePrefix="1" borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5B3F86"/>
+          <bgColor rgb="FF5B3F86"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8F9FA"/>
           <bgColor rgb="FFF8F9FA"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF5B3F86"/>
-          <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
+      <border/>
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="Form Responses 1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+    <tableStyle count="3" pivot="0" name="Form Responses 1-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses1" displayName="Form_Responses1" ref="A1:H37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H38" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Timestamp"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="First Name"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Last Name"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Other Names"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Email Address"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Phone Number"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Feedback"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Feedback Order"/>
+    <tableColumn name="Timestamp" id="1"/>
+    <tableColumn name="First Name" id="2"/>
+    <tableColumn name="Last Name" id="3"/>
+    <tableColumn name="Other Names" id="4"/>
+    <tableColumn name="Email Address" id="5"/>
+    <tableColumn name="Phone Number" id="6"/>
+    <tableColumn name="Feedback" id="7"/>
+    <tableColumn name="Feedback Order" id="8"/>
   </tableColumns>
-  <tableStyleInfo name="Form Responses 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="Form Responses 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1089,25 +1129,22 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="37.6640625" customWidth="1"/>
-    <col min="8" max="14" width="18.83203125" customWidth="1"/>
+    <col customWidth="1" min="1" max="6" width="18.88"/>
+    <col customWidth="1" min="7" max="7" width="37.75"/>
+    <col customWidth="1" min="8" max="14" width="18.88"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1126,763 +1163,783 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="4">
+    <row r="2">
+      <c r="A2" s="5">
         <v>45728.821473171294</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="8">
+      <c r="G2" s="8"/>
+      <c r="H2" s="9"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="10">
         <v>45729.213411793986</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="11"/>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="4">
-        <v>45729.266961550922</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="G3" s="13"/>
+      <c r="H3" s="14"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="15">
+        <v>45729.26696155092</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="8">
-        <v>45729.326776678237</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="G4" s="8"/>
+      <c r="H4" s="9"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10">
+        <v>45729.32677667824</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="11"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="4">
-        <v>45729.538555370367</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="G5" s="13"/>
+      <c r="H5" s="14"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="15">
+        <v>45729.53855537037</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="8">
-        <v>45729.541992719911</v>
-      </c>
-      <c r="B7" s="9" t="s">
+      <c r="G6" s="8"/>
+      <c r="H6" s="9"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10">
+        <v>45729.54199271991</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="4">
-        <v>45729.984873564812</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="H7" s="19">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15">
+        <v>45729.98487356481</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="8">
-        <v>45736.660632384257</v>
-      </c>
-      <c r="B9" s="9" t="s">
+      <c r="G8" s="8"/>
+      <c r="H8" s="9"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10">
+        <v>45736.66063238426</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="11"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="4">
-        <v>45736.729689363427</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="G9" s="13"/>
+      <c r="H9" s="14"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15">
+        <v>45736.72968936343</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="8">
-        <v>45736.732069120371</v>
-      </c>
-      <c r="B11" s="9" t="s">
+      <c r="G10" s="8"/>
+      <c r="H10" s="9"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10">
+        <v>45736.73206912037</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="4">
+      <c r="H11" s="19">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15">
         <v>45736.7642705787</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="H12" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="8">
-        <v>45736.952224409717</v>
-      </c>
-      <c r="B13" s="9" t="s">
+      <c r="H12" s="22">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10">
+        <v>45736.95222440972</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="11"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="4">
-        <v>45736.999104432871</v>
-      </c>
-      <c r="B14" s="5" t="s">
+      <c r="G13" s="23"/>
+      <c r="H13" s="14"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15">
+        <v>45736.99910443287</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5" t="s">
+      <c r="D14" s="16"/>
+      <c r="E14" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="H14" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="8">
-        <v>45737.326202465279</v>
-      </c>
-      <c r="B15" s="9" t="s">
+      <c r="H14" s="22">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10">
+        <v>45737.32620246528</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="G15" s="12"/>
-      <c r="H15" s="11"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="4">
-        <v>45737.605513715273</v>
-      </c>
-      <c r="B16" s="5" t="s">
+      <c r="G15" s="23"/>
+      <c r="H15" s="14"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15">
+        <v>45737.60551371527</v>
+      </c>
+      <c r="B16" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="8">
+      <c r="G16" s="24"/>
+      <c r="H16" s="9"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10">
         <v>45738.71291584491</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="G17" s="12"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="4">
-        <v>45738.713462800923</v>
-      </c>
-      <c r="B18" s="5" t="s">
+      <c r="G17" s="25"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15">
+        <v>45738.71346280092</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="G18" s="13"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="8">
-        <v>45738.717408703698</v>
-      </c>
-      <c r="B19" s="9" t="s">
+      <c r="G18" s="26"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10">
+        <v>45738.7174087037</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="G19" s="12"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="4">
+      <c r="G19" s="25"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15">
         <v>45738.718439131946</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="G20" s="13"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="8">
-        <v>45739.507987442128</v>
-      </c>
-      <c r="B21" s="9" t="s">
+      <c r="G20" s="26"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10">
+        <v>45739.50798744213</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="G21" s="12"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="4">
-        <v>45739.517761550931</v>
-      </c>
-      <c r="B22" s="5" t="s">
+      <c r="G21" s="25"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15">
+        <v>45739.51776155093</v>
+      </c>
+      <c r="B22" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="G22" s="13" t="s">
+      <c r="G22" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="H22" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="8">
-        <v>45739.573868715277</v>
-      </c>
-      <c r="B23" s="9" t="s">
+      <c r="H22" s="28">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10">
+        <v>45739.57386871528</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="H23" s="11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="4">
-        <v>45739.590264699073</v>
-      </c>
-      <c r="B24" s="5" t="s">
+      <c r="H23" s="30">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15">
+        <v>45739.59026469907</v>
+      </c>
+      <c r="B24" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="17" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="8">
-        <v>45739.607103287039</v>
-      </c>
-      <c r="B25" s="9" t="s">
+    <row r="25">
+      <c r="A25" s="10">
+        <v>45739.60710328704</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="4">
+    <row r="26">
+      <c r="A26" s="15">
         <v>45742.417584131945</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="17" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="8">
-        <v>45742.643638935187</v>
-      </c>
-      <c r="B27" s="9" t="s">
+    <row r="27">
+      <c r="A27" s="10">
+        <v>45742.64363893519</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="12" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="4">
-        <v>45742.896631307871</v>
-      </c>
-      <c r="B28" s="5" t="s">
+    <row r="28">
+      <c r="A28" s="15">
+        <v>45742.89663130787</v>
+      </c>
+      <c r="B28" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="17" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="8">
+    <row r="29">
+      <c r="A29" s="10">
         <v>45743.999212106486</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="12" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="4">
+    <row r="30">
+      <c r="A30" s="15">
         <v>45745.549431770836</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="17" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="8">
-        <v>45747.629571608792</v>
-      </c>
-      <c r="B31" s="9" t="s">
+    <row r="31">
+      <c r="A31" s="10">
+        <v>45747.62957160879</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9" t="s">
+      <c r="D31" s="11"/>
+      <c r="E31" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="12" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="4">
-        <v>45755.831486620373</v>
-      </c>
-      <c r="B32" s="5" t="s">
+    <row r="32">
+      <c r="A32" s="15">
+        <v>45755.83148662037</v>
+      </c>
+      <c r="B32" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="17" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="8">
-        <v>45755.833264895831</v>
-      </c>
-      <c r="B33" s="9" t="s">
+    <row r="33">
+      <c r="A33" s="10">
+        <v>45755.83326489583</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" s="12" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="4">
-        <v>45755.833779282402</v>
-      </c>
-      <c r="B34" s="5" t="s">
+    <row r="34">
+      <c r="A34" s="15">
+        <v>45755.8337792824</v>
+      </c>
+      <c r="B34" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="17" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="8">
-        <v>45762.839534942133</v>
-      </c>
-      <c r="B35" s="9" t="s">
+    <row r="35">
+      <c r="A35" s="10">
+        <v>45762.83953494213</v>
+      </c>
+      <c r="B35" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="D35" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15">
+        <v>45763.48679163195</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10">
+        <v>45774.85872887731</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F37" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="E35" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="4">
-        <v>45763.486791631949</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="14">
-        <v>45774.858728877312</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="F37" s="15" t="s">
-        <v>178</v>
+    </row>
+    <row r="38">
+      <c r="A38" s="31">
+        <v>45776.87331313657</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="D38" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="E38" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="188">
   <si>
     <t>Timestamp</t>
   </si>
@@ -572,6 +572,18 @@
   </si>
   <si>
     <t>0710985400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ephantus </t>
+  </si>
+  <si>
+    <t>Kihiko</t>
+  </si>
+  <si>
+    <t>ekihikomaina@gmail.com</t>
+  </si>
+  <si>
+    <t>0726929344</t>
   </si>
 </sst>
 </file>
@@ -735,10 +747,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -746,13 +758,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -923,7 +935,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H38" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H39" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -1917,23 +1929,40 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="31">
+      <c r="A38" s="15">
         <v>45776.87331313657</v>
       </c>
-      <c r="B38" s="32" t="s">
+      <c r="B38" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C38" s="32" t="s">
+      <c r="C38" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="D38" s="32" t="s">
+      <c r="D38" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="E38" s="32" t="s">
+      <c r="E38" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="F38" s="33" t="s">
+      <c r="F38" s="17" t="s">
         <v>183</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="31">
+        <v>45777.19636966435</v>
+      </c>
+      <c r="B39" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="C39" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="193">
   <si>
     <t>Timestamp</t>
   </si>
@@ -229,7 +229,7 @@
     <t>0742439127</t>
   </si>
   <si>
-    <t>Hey Miller, I've interacted with the app, it's pretty easy,keep up the great work.</t>
+    <t>Hey Miller, I've interacted with the app, it's pretty easy, keep up the great work.</t>
   </si>
   <si>
     <t xml:space="preserve">Mary Gloria </t>
@@ -584,6 +584,21 @@
   </si>
   <si>
     <t>0726929344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beatrice </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ndung'u </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wambui </t>
+  </si>
+  <si>
+    <t>wambuindungu12m@gmail.com</t>
+  </si>
+  <si>
+    <t>0794766801</t>
   </si>
 </sst>
 </file>
@@ -747,10 +762,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -758,13 +773,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -935,7 +950,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H39" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H40" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -1949,20 +1964,40 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="31">
+      <c r="A39" s="10">
         <v>45777.19636966435</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="C39" s="32" t="s">
+      <c r="C39" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="E39" s="32" t="s">
+      <c r="E39" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="F39" s="33" t="s">
+      <c r="F39" s="12" t="s">
         <v>187</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="31">
+        <v>45778.45970409722</v>
+      </c>
+      <c r="B40" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="C40" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="D40" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="E40" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="F40" s="33" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="198">
   <si>
     <t>Timestamp</t>
   </si>
@@ -599,6 +599,21 @@
   </si>
   <si>
     <t>0794766801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nancy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ndeti </t>
+  </si>
+  <si>
+    <t>Lisi</t>
+  </si>
+  <si>
+    <t>Lisi.ndeti@hotmail.com</t>
+  </si>
+  <si>
+    <t>0738468745</t>
   </si>
 </sst>
 </file>
@@ -762,10 +777,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -773,13 +788,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -950,7 +965,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H40" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H41" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -1981,23 +1996,43 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="31">
+      <c r="A40" s="15">
         <v>45778.45970409722</v>
       </c>
-      <c r="B40" s="32" t="s">
+      <c r="B40" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="C40" s="32" t="s">
+      <c r="C40" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="E40" s="32" t="s">
+      <c r="E40" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="F40" s="33" t="s">
+      <c r="F40" s="17" t="s">
         <v>192</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="31">
+        <v>45778.60069641204</v>
+      </c>
+      <c r="B41" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C41" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="D41" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="E41" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="F41" s="33" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="202">
   <si>
     <t>Timestamp</t>
   </si>
@@ -614,6 +614,18 @@
   </si>
   <si>
     <t>0738468745</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>Wanyeki</t>
+  </si>
+  <si>
+    <t>wanyekimartin100@gmail.com</t>
+  </si>
+  <si>
+    <t>0727023746</t>
   </si>
 </sst>
 </file>
@@ -777,10 +789,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -788,13 +800,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -965,7 +977,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H41" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H42" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2016,23 +2028,40 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="31">
+      <c r="A41" s="10">
         <v>45778.60069641204</v>
       </c>
-      <c r="B41" s="32" t="s">
+      <c r="B41" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="C41" s="32" t="s">
+      <c r="C41" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="D41" s="32" t="s">
+      <c r="D41" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="E41" s="32" t="s">
+      <c r="E41" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="F41" s="33" t="s">
+      <c r="F41" s="12" t="s">
         <v>197</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="31">
+        <v>45779.645806053246</v>
+      </c>
+      <c r="B42" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="E42" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="F42" s="33" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="216">
   <si>
     <t>Timestamp</t>
   </si>
@@ -626,6 +626,48 @@
   </si>
   <si>
     <t>0727023746</t>
+  </si>
+  <si>
+    <t>Hannah</t>
+  </si>
+  <si>
+    <t>Wanjiku</t>
+  </si>
+  <si>
+    <t>shikuwaimani@gmail.com</t>
+  </si>
+  <si>
+    <t>0728594505</t>
+  </si>
+  <si>
+    <t>Neema</t>
+  </si>
+  <si>
+    <t>Muthoki</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>muthokineema26@gmail.com</t>
+  </si>
+  <si>
+    <t>0704830604</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>Musyoka</t>
+  </si>
+  <si>
+    <t>Muuo</t>
+  </si>
+  <si>
+    <t>Musyokakevin06@gmail.com</t>
+  </si>
+  <si>
+    <t>0711687123</t>
   </si>
 </sst>
 </file>
@@ -789,10 +831,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -800,13 +842,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -977,7 +1019,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H42" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H45" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2048,20 +2090,77 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="31">
+      <c r="A42" s="15">
         <v>45779.645806053246</v>
       </c>
-      <c r="B42" s="32" t="s">
+      <c r="B42" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="C42" s="32" t="s">
+      <c r="C42" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="E42" s="32" t="s">
+      <c r="E42" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="F42" s="33" t="s">
+      <c r="F42" s="17" t="s">
         <v>201</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10">
+        <v>45779.92289221065</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15">
+        <v>45783.43115336806</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="31">
+        <v>45783.82635567129</v>
+      </c>
+      <c r="B45" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="C45" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="D45" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="E45" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="F45" s="33" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="219">
   <si>
     <t>Timestamp</t>
   </si>
@@ -668,6 +668,15 @@
   </si>
   <si>
     <t>0711687123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Susan </t>
+  </si>
+  <si>
+    <t>suzzsheba@gmail.com</t>
+  </si>
+  <si>
+    <t>0702862276</t>
   </si>
 </sst>
 </file>
@@ -831,10 +840,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -842,13 +851,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1019,7 +1028,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H45" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H46" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2144,23 +2153,40 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="31">
+      <c r="A45" s="10">
         <v>45783.82635567129</v>
       </c>
-      <c r="B45" s="32" t="s">
+      <c r="B45" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C45" s="32" t="s">
+      <c r="C45" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="D45" s="32" t="s">
+      <c r="D45" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="E45" s="32" t="s">
+      <c r="E45" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="F45" s="33" t="s">
+      <c r="F45" s="12" t="s">
         <v>215</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="31">
+        <v>45786.020762291664</v>
+      </c>
+      <c r="B46" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="F46" s="33" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="224">
   <si>
     <t>Timestamp</t>
   </si>
@@ -677,6 +677,21 @@
   </si>
   <si>
     <t>0702862276</t>
+  </si>
+  <si>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murugi </t>
+  </si>
+  <si>
+    <t>Baru</t>
+  </si>
+  <si>
+    <t>sarahbaru9@gmail.com</t>
+  </si>
+  <si>
+    <t>0708490643</t>
   </si>
 </sst>
 </file>
@@ -840,10 +855,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -851,13 +866,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1028,7 +1043,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H46" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H47" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2173,20 +2188,40 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="31">
+      <c r="A46" s="15">
         <v>45786.020762291664</v>
       </c>
-      <c r="B46" s="32" t="s">
+      <c r="B46" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="C46" s="32" t="s">
+      <c r="C46" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E46" s="32" t="s">
+      <c r="E46" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="F46" s="33" t="s">
+      <c r="F46" s="17" t="s">
         <v>218</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="31">
+        <v>45788.53713011574</v>
+      </c>
+      <c r="B47" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="D47" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E47" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="F47" s="33" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="254">
   <si>
     <t>Timestamp</t>
   </si>
@@ -692,6 +692,96 @@
   </si>
   <si>
     <t>0708490643</t>
+  </si>
+  <si>
+    <t>Kimani</t>
+  </si>
+  <si>
+    <t>marykimani01@gmail.com</t>
+  </si>
+  <si>
+    <t>0716423140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elvis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tsiavoga </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunayo </t>
+  </si>
+  <si>
+    <t>elvistsiavoga@gmail.com</t>
+  </si>
+  <si>
+    <t>0706665577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marceline </t>
+  </si>
+  <si>
+    <t>Mukok</t>
+  </si>
+  <si>
+    <t>Awuor</t>
+  </si>
+  <si>
+    <t>lornamercy715@gmail.com</t>
+  </si>
+  <si>
+    <t>0717797348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kelvin </t>
+  </si>
+  <si>
+    <t>Muthiikm@gmail.com</t>
+  </si>
+  <si>
+    <t>0708679675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agwona </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahkings </t>
+  </si>
+  <si>
+    <t>elvisagwona9@gmail.com</t>
+  </si>
+  <si>
+    <t>0748412482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victor </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oluoch </t>
+  </si>
+  <si>
+    <t>Ochienh</t>
+  </si>
+  <si>
+    <t>oluochivictor11@gmail.com</t>
+  </si>
+  <si>
+    <t>0743857509</t>
+  </si>
+  <si>
+    <t>Fridah</t>
+  </si>
+  <si>
+    <t>Namu</t>
+  </si>
+  <si>
+    <t>Murugi</t>
+  </si>
+  <si>
+    <t>fridahnamu@yahoo.com</t>
+  </si>
+  <si>
+    <t>0711704441</t>
   </si>
 </sst>
 </file>
@@ -855,10 +945,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -866,13 +956,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1043,7 +1133,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H47" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H54" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2205,23 +2295,157 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="31">
+      <c r="A47" s="10">
         <v>45788.53713011574</v>
       </c>
-      <c r="B47" s="32" t="s">
+      <c r="B47" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="C47" s="32" t="s">
+      <c r="C47" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="D47" s="32" t="s">
+      <c r="D47" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="E47" s="32" t="s">
+      <c r="E47" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="F47" s="33" t="s">
+      <c r="F47" s="12" t="s">
         <v>223</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15">
+        <v>45790.439616828706</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10">
+        <v>45790.81482274305</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15">
+        <v>45790.81510371528</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10">
+        <v>45790.81564590278</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15">
+        <v>45790.818043182866</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="F52" s="17" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10">
+        <v>45790.8186880787</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="31">
+        <v>45790.819839641204</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="C54" s="32" t="s">
+        <v>250</v>
+      </c>
+      <c r="D54" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="E54" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="F54" s="33" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="259">
   <si>
     <t>Timestamp</t>
   </si>
@@ -782,6 +782,21 @@
   </si>
   <si>
     <t>0711704441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bravin </t>
+  </si>
+  <si>
+    <t>Sakari</t>
+  </si>
+  <si>
+    <t>Mechi</t>
+  </si>
+  <si>
+    <t>bravinsakari@gmail.com</t>
+  </si>
+  <si>
+    <t>0745655703</t>
   </si>
 </sst>
 </file>
@@ -945,10 +960,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -956,13 +971,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1133,7 +1148,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H54" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H55" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2429,23 +2444,43 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="31">
+      <c r="A54" s="15">
         <v>45790.819839641204</v>
       </c>
-      <c r="B54" s="32" t="s">
+      <c r="B54" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="C54" s="32" t="s">
+      <c r="C54" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="D54" s="32" t="s">
+      <c r="D54" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="E54" s="32" t="s">
+      <c r="E54" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="F54" s="33" t="s">
+      <c r="F54" s="17" t="s">
         <v>253</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="31">
+        <v>45790.82116704861</v>
+      </c>
+      <c r="B55" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="C55" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="D55" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="E55" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="F55" s="33" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="268">
   <si>
     <t>Timestamp</t>
   </si>
@@ -742,6 +742,9 @@
     <t>0708679675</t>
   </si>
   <si>
+    <t>Setup on Huawei</t>
+  </si>
+  <si>
     <t xml:space="preserve">Agwona </t>
   </si>
   <si>
@@ -797,6 +800,30 @@
   </si>
   <si>
     <t>0745655703</t>
+  </si>
+  <si>
+    <t>Job</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ong'ang'a</t>
+  </si>
+  <si>
+    <t>Ongangaj6@gmail.com</t>
+  </si>
+  <si>
+    <t>0111272146</t>
+  </si>
+  <si>
+    <t>Brighton</t>
+  </si>
+  <si>
+    <t>Omondi</t>
+  </si>
+  <si>
+    <t>probrighton@gmail.com</t>
+  </si>
+  <si>
+    <t>+254727727302</t>
   </si>
 </sst>
 </file>
@@ -987,7 +1014,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1085,9 +1112,6 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf quotePrefix="1" borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -1148,7 +1172,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H55" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H57" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2402,6 +2426,9 @@
       <c r="F51" s="12" t="s">
         <v>239</v>
       </c>
+      <c r="G51" s="11" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="15">
@@ -2411,16 +2438,16 @@
         <v>227</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F52" s="17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="53">
@@ -2428,19 +2455,19 @@
         <v>45790.8186880787</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="54">
@@ -2448,39 +2475,75 @@
         <v>45790.819839641204</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F54" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="31">
+      <c r="A55" s="10">
         <v>45790.82116704861</v>
       </c>
-      <c r="B55" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="C55" s="32" t="s">
+      <c r="B55" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="D55" s="32" t="s">
+      <c r="C55" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="E55" s="32" t="s">
+      <c r="D55" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="F55" s="33" t="s">
+      <c r="E55" s="11" t="s">
         <v>258</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15">
+        <v>45790.829695381944</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="D56" s="16"/>
+      <c r="E56" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="F56" s="17" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="31">
+        <v>45790.83051489583</v>
+      </c>
+      <c r="B57" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="C57" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="F57" s="32" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="272">
   <si>
     <t>Timestamp</t>
   </si>
@@ -824,6 +824,18 @@
   </si>
   <si>
     <t>+254727727302</t>
+  </si>
+  <si>
+    <t>Becky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilberforce </t>
+  </si>
+  <si>
+    <t>rebmuli66@gmail.com</t>
+  </si>
+  <si>
+    <t>0729470877</t>
   </si>
 </sst>
 </file>
@@ -987,10 +999,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -998,13 +1010,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1014,7 +1026,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1112,6 +1124,9 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf quotePrefix="1" borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -1172,7 +1187,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H57" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H58" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2529,21 +2544,38 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="31">
+      <c r="A57" s="10">
         <v>45790.83051489583</v>
       </c>
-      <c r="B57" s="32" t="s">
+      <c r="B57" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="C57" s="32" t="s">
+      <c r="C57" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="D57" s="32"/>
-      <c r="E57" s="32" t="s">
+      <c r="D57" s="11"/>
+      <c r="E57" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="F57" s="32" t="s">
+      <c r="F57" s="11" t="s">
         <v>267</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="31">
+        <v>45791.457139606486</v>
+      </c>
+      <c r="B58" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="C58" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="E58" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="F58" s="33" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="277">
   <si>
     <t>Timestamp</t>
   </si>
@@ -805,7 +805,7 @@
     <t>Job</t>
   </si>
   <si>
-    <t xml:space="preserve"> Ong'ang'a</t>
+    <t>Ong'ang'a</t>
   </si>
   <si>
     <t>Ongangaj6@gmail.com</t>
@@ -836,6 +836,21 @@
   </si>
   <si>
     <t>0729470877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brenda </t>
+  </si>
+  <si>
+    <t>Kamau</t>
+  </si>
+  <si>
+    <t>Nyambura</t>
+  </si>
+  <si>
+    <t>brendakamau19@gmail.com</t>
+  </si>
+  <si>
+    <t>0725061903</t>
   </si>
 </sst>
 </file>
@@ -999,10 +1014,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1010,13 +1025,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1187,7 +1202,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H58" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H59" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2562,20 +2577,40 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="31">
+      <c r="A58" s="15">
         <v>45791.457139606486</v>
       </c>
-      <c r="B58" s="32" t="s">
+      <c r="B58" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="C58" s="32" t="s">
+      <c r="C58" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="E58" s="32" t="s">
+      <c r="E58" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="F58" s="33" t="s">
+      <c r="F58" s="17" t="s">
         <v>271</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="31">
+        <v>45794.447150023145</v>
+      </c>
+      <c r="B59" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="C59" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="D59" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="E59" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="F59" s="33" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="281">
   <si>
     <t>Timestamp</t>
   </si>
@@ -851,6 +851,18 @@
   </si>
   <si>
     <t>0725061903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faith </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wanjiku </t>
+  </si>
+  <si>
+    <t>faithmwangi255@gmail.com</t>
+  </si>
+  <si>
+    <t>0792907575</t>
   </si>
 </sst>
 </file>
@@ -1014,10 +1026,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1025,13 +1037,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1202,7 +1214,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H59" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H60" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2594,23 +2606,43 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="31">
+      <c r="A59" s="10">
         <v>45794.447150023145</v>
       </c>
-      <c r="B59" s="32" t="s">
+      <c r="B59" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="C59" s="32" t="s">
+      <c r="C59" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="D59" s="32" t="s">
+      <c r="D59" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="E59" s="32" t="s">
+      <c r="E59" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="F59" s="33" t="s">
+      <c r="F59" s="12" t="s">
         <v>276</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="31">
+        <v>45797.46449648148</v>
+      </c>
+      <c r="B60" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="C60" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="D60" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="E60" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="F60" s="33" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="286">
   <si>
     <t>Timestamp</t>
   </si>
@@ -863,6 +863,21 @@
   </si>
   <si>
     <t>0792907575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dinel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Njoroge </t>
+  </si>
+  <si>
+    <t>Wangari</t>
+  </si>
+  <si>
+    <t>dinelnjoroge@gmail.com</t>
+  </si>
+  <si>
+    <t>+254742829462</t>
   </si>
 </sst>
 </file>
@@ -1026,10 +1041,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1037,13 +1052,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1053,7 +1068,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1151,9 +1166,6 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf quotePrefix="1" borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -1214,7 +1226,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H60" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H61" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2626,23 +2638,43 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="31">
+      <c r="A60" s="15">
         <v>45797.46449648148</v>
       </c>
-      <c r="B60" s="32" t="s">
+      <c r="B60" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="C60" s="32" t="s">
+      <c r="C60" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="D60" s="32" t="s">
+      <c r="D60" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="E60" s="32" t="s">
+      <c r="E60" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="F60" s="33" t="s">
+      <c r="F60" s="17" t="s">
         <v>280</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="31">
+        <v>45797.619680358795</v>
+      </c>
+      <c r="B61" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="C61" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="D61" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="E61" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="F61" s="32" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="290">
   <si>
     <t>Timestamp</t>
   </si>
@@ -878,6 +878,18 @@
   </si>
   <si>
     <t>+254742829462</t>
+  </si>
+  <si>
+    <t>Kavata</t>
+  </si>
+  <si>
+    <t>Nyamai</t>
+  </si>
+  <si>
+    <t>gracekavata07@gmail.com</t>
+  </si>
+  <si>
+    <t>+254721420410</t>
   </si>
 </sst>
 </file>
@@ -1041,10 +1053,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1052,13 +1064,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1226,7 +1238,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H61" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H62" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2658,23 +2670,43 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="31">
+      <c r="A61" s="10">
         <v>45797.619680358795</v>
       </c>
-      <c r="B61" s="32" t="s">
+      <c r="B61" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="C61" s="32" t="s">
+      <c r="C61" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="D61" s="32" t="s">
+      <c r="D61" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="E61" s="32" t="s">
+      <c r="E61" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="F61" s="32" t="s">
+      <c r="F61" s="11" t="s">
         <v>285</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="31">
+        <v>45798.40113211806</v>
+      </c>
+      <c r="B62" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="C62" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="D62" s="32" t="s">
+        <v>287</v>
+      </c>
+      <c r="E62" s="32" t="s">
+        <v>288</v>
+      </c>
+      <c r="F62" s="32" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="294">
   <si>
     <t>Timestamp</t>
   </si>
@@ -890,6 +890,18 @@
   </si>
   <si>
     <t>+254721420410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James </t>
+  </si>
+  <si>
+    <t>Ndiangui</t>
+  </si>
+  <si>
+    <t>Jndiangui@gmail.com</t>
+  </si>
+  <si>
+    <t>+254737411700</t>
   </si>
 </sst>
 </file>
@@ -1053,10 +1065,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1064,13 +1076,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1238,7 +1250,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H62" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H63" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2690,23 +2702,40 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="31">
+      <c r="A62" s="15">
         <v>45798.40113211806</v>
       </c>
-      <c r="B62" s="32" t="s">
+      <c r="B62" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C62" s="32" t="s">
+      <c r="C62" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="D62" s="32" t="s">
+      <c r="D62" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="E62" s="32" t="s">
+      <c r="E62" s="16" t="s">
         <v>288</v>
       </c>
-      <c r="F62" s="32" t="s">
+      <c r="F62" s="16" t="s">
         <v>289</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="31">
+        <v>45802.90266039352</v>
+      </c>
+      <c r="B63" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="C63" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="E63" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="F63" s="32" t="s">
+        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="298">
   <si>
     <t>Timestamp</t>
   </si>
@@ -902,6 +902,18 @@
   </si>
   <si>
     <t>+254737411700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carolyne </t>
+  </si>
+  <si>
+    <t>Rahab</t>
+  </si>
+  <si>
+    <t>carolrahab01@gmail.com</t>
+  </si>
+  <si>
+    <t>0788884515</t>
   </si>
 </sst>
 </file>
@@ -1065,10 +1077,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1076,13 +1088,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1092,7 +1104,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1190,6 +1202,9 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf quotePrefix="1" borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -1250,7 +1265,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H63" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H64" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2722,20 +2737,37 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="31">
+      <c r="A63" s="10">
         <v>45802.90266039352</v>
       </c>
-      <c r="B63" s="32" t="s">
+      <c r="B63" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="C63" s="32" t="s">
+      <c r="C63" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="E63" s="32" t="s">
+      <c r="E63" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="F63" s="32" t="s">
+      <c r="F63" s="11" t="s">
         <v>293</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="31">
+        <v>45805.897863148144</v>
+      </c>
+      <c r="B64" s="32" t="s">
+        <v>294</v>
+      </c>
+      <c r="C64" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="E64" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="F64" s="33" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="312">
   <si>
     <t>Timestamp</t>
   </si>
@@ -907,13 +907,55 @@
     <t xml:space="preserve">Carolyne </t>
   </si>
   <si>
-    <t>Rahab</t>
-  </si>
-  <si>
     <t>carolrahab01@gmail.com</t>
   </si>
   <si>
     <t>0788884515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rasoa </t>
+  </si>
+  <si>
+    <t>Nekesa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omondi </t>
+  </si>
+  <si>
+    <t>rasnekesa@gmail.com</t>
+  </si>
+  <si>
+    <t>0726966650</t>
+  </si>
+  <si>
+    <t>Samuel</t>
+  </si>
+  <si>
+    <t>Mukui</t>
+  </si>
+  <si>
+    <t>Chege</t>
+  </si>
+  <si>
+    <t>chege.mukui@gmail.com</t>
+  </si>
+  <si>
+    <t>0719500900</t>
+  </si>
+  <si>
+    <t>Romano</t>
+  </si>
+  <si>
+    <t>Wamalwa</t>
+  </si>
+  <si>
+    <t>Wanjala</t>
+  </si>
+  <si>
+    <t>romanowamalwa363@gmail.com</t>
+  </si>
+  <si>
+    <t>0722538882</t>
   </si>
 </sst>
 </file>
@@ -1077,10 +1119,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1088,13 +1130,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1265,7 +1307,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H64" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H67" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2754,20 +2796,80 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="31">
+      <c r="A64" s="15">
         <v>45805.897863148144</v>
       </c>
-      <c r="B64" s="32" t="s">
+      <c r="B64" s="16" t="s">
         <v>294</v>
       </c>
-      <c r="C64" s="32" t="s">
+      <c r="C64" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="E64" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="E64" s="32" t="s">
+      <c r="F64" s="17" t="s">
         <v>296</v>
       </c>
-      <c r="F64" s="33" t="s">
+    </row>
+    <row r="65">
+      <c r="A65" s="10">
+        <v>45810.627454710644</v>
+      </c>
+      <c r="B65" s="11" t="s">
         <v>297</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="15">
+        <v>45810.833673125</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="D66" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31">
+        <v>45811.757312534726</v>
+      </c>
+      <c r="B67" s="32" t="s">
+        <v>307</v>
+      </c>
+      <c r="C67" s="32" t="s">
+        <v>308</v>
+      </c>
+      <c r="D67" s="32" t="s">
+        <v>309</v>
+      </c>
+      <c r="E67" s="32" t="s">
+        <v>310</v>
+      </c>
+      <c r="F67" s="33" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="315">
   <si>
     <t>Timestamp</t>
   </si>
@@ -956,6 +956,15 @@
   </si>
   <si>
     <t>0722538882</t>
+  </si>
+  <si>
+    <t>Winnie</t>
+  </si>
+  <si>
+    <t>wimutua@gmail.com</t>
+  </si>
+  <si>
+    <t>0711698629</t>
   </si>
 </sst>
 </file>
@@ -1119,10 +1128,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1130,13 +1139,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1307,7 +1316,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H67" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H68" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2853,23 +2862,40 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="31">
+      <c r="A67" s="10">
         <v>45811.757312534726</v>
       </c>
-      <c r="B67" s="32" t="s">
+      <c r="B67" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="C67" s="32" t="s">
+      <c r="C67" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="D67" s="32" t="s">
+      <c r="D67" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="E67" s="32" t="s">
+      <c r="E67" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="F67" s="33" t="s">
+      <c r="F67" s="12" t="s">
         <v>311</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="31">
+        <v>45813.84342119213</v>
+      </c>
+      <c r="B68" s="32" t="s">
+        <v>312</v>
+      </c>
+      <c r="C68" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="E68" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="F68" s="33" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="319">
   <si>
     <t>Timestamp</t>
   </si>
@@ -965,6 +965,18 @@
   </si>
   <si>
     <t>0711698629</t>
+  </si>
+  <si>
+    <t>Jackson</t>
+  </si>
+  <si>
+    <t>Macharia</t>
+  </si>
+  <si>
+    <t>jmpiranhajack@gmail.com</t>
+  </si>
+  <si>
+    <t>0721725753</t>
   </si>
 </sst>
 </file>
@@ -1128,10 +1140,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1139,13 +1151,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1316,7 +1328,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H68" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H69" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2882,20 +2894,37 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="31">
+      <c r="A68" s="15">
         <v>45813.84342119213</v>
       </c>
-      <c r="B68" s="32" t="s">
+      <c r="B68" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="C68" s="32" t="s">
+      <c r="C68" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="E68" s="32" t="s">
+      <c r="E68" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="F68" s="33" t="s">
+      <c r="F68" s="17" t="s">
         <v>314</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="31">
+        <v>45814.448951053244</v>
+      </c>
+      <c r="B69" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="C69" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="E69" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="F69" s="33" t="s">
+        <v>318</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="326">
   <si>
     <t>Timestamp</t>
   </si>
@@ -977,6 +977,27 @@
   </si>
   <si>
     <t>0721725753</t>
+  </si>
+  <si>
+    <t>Victoria</t>
+  </si>
+  <si>
+    <t>victoriagithii99@gmail.com</t>
+  </si>
+  <si>
+    <t>0799786238</t>
+  </si>
+  <si>
+    <t>Musungu</t>
+  </si>
+  <si>
+    <t>Lesly</t>
+  </si>
+  <si>
+    <t>musunguarthur29@gmail.com</t>
+  </si>
+  <si>
+    <t>0721451164</t>
   </si>
 </sst>
 </file>
@@ -1328,7 +1349,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H69" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H71" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2911,20 +2932,57 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="31">
+      <c r="A69" s="10">
         <v>45814.448951053244</v>
       </c>
-      <c r="B69" s="32" t="s">
+      <c r="B69" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="C69" s="32" t="s">
+      <c r="C69" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="E69" s="32" t="s">
+      <c r="E69" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="F69" s="33" t="s">
+      <c r="F69" s="12" t="s">
         <v>318</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="15">
+        <v>45814.482309687504</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E70" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="F70" s="17" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31">
+        <v>45814.54972652778</v>
+      </c>
+      <c r="B71" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="D71" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="E71" s="32" t="s">
+        <v>324</v>
+      </c>
+      <c r="F71" s="33" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="331">
   <si>
     <t>Timestamp</t>
   </si>
@@ -998,6 +998,21 @@
   </si>
   <si>
     <t>0721451164</t>
+  </si>
+  <si>
+    <t>Shikoh</t>
+  </si>
+  <si>
+    <t>Masika</t>
+  </si>
+  <si>
+    <t>Gacheru</t>
+  </si>
+  <si>
+    <t>gracegacheru@gmail.com</t>
+  </si>
+  <si>
+    <t>0726289244</t>
   </si>
 </sst>
 </file>
@@ -1161,10 +1176,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1172,13 +1187,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1349,7 +1364,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H71" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H72" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -2966,23 +2981,43 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="31">
+      <c r="A71" s="10">
         <v>45814.54972652778</v>
       </c>
-      <c r="B71" s="32" t="s">
+      <c r="B71" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C71" s="32" t="s">
+      <c r="C71" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="D71" s="32" t="s">
+      <c r="D71" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="E71" s="32" t="s">
+      <c r="E71" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="F71" s="33" t="s">
+      <c r="F71" s="12" t="s">
         <v>325</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31">
+        <v>45814.88585548611</v>
+      </c>
+      <c r="B72" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="C72" s="32" t="s">
+        <v>327</v>
+      </c>
+      <c r="D72" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="E72" s="32" t="s">
+        <v>329</v>
+      </c>
+      <c r="F72" s="33" t="s">
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="338">
   <si>
     <t>Timestamp</t>
   </si>
@@ -1013,6 +1013,27 @@
   </si>
   <si>
     <t>0726289244</t>
+  </si>
+  <si>
+    <t>Joan</t>
+  </si>
+  <si>
+    <t>joannyawira046@gmail.com</t>
+  </si>
+  <si>
+    <t>0726887800</t>
+  </si>
+  <si>
+    <t>Randy</t>
+  </si>
+  <si>
+    <t>Marlon</t>
+  </si>
+  <si>
+    <t>randymarlon1095@gmail.com</t>
+  </si>
+  <si>
+    <t>0110129659</t>
   </si>
 </sst>
 </file>
@@ -1364,7 +1385,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H72" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H74" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -3001,23 +3022,57 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="31">
+      <c r="A72" s="15">
         <v>45814.88585548611</v>
       </c>
-      <c r="B72" s="32" t="s">
+      <c r="B72" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="C72" s="32" t="s">
+      <c r="C72" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="D72" s="32" t="s">
+      <c r="D72" s="16" t="s">
         <v>328</v>
       </c>
-      <c r="E72" s="32" t="s">
+      <c r="E72" s="16" t="s">
         <v>329</v>
       </c>
-      <c r="F72" s="33" t="s">
+      <c r="F72" s="17" t="s">
         <v>330</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10">
+        <v>45816.68014175926</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31">
+        <v>45817.48228399306</v>
+      </c>
+      <c r="B74" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="C74" s="32" t="s">
+        <v>335</v>
+      </c>
+      <c r="E74" s="32" t="s">
+        <v>336</v>
+      </c>
+      <c r="F74" s="33" t="s">
+        <v>337</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="346">
   <si>
     <t>Timestamp</t>
   </si>
@@ -1034,6 +1034,30 @@
   </si>
   <si>
     <t>0110129659</t>
+  </si>
+  <si>
+    <t>Sheila</t>
+  </si>
+  <si>
+    <t>Ngui</t>
+  </si>
+  <si>
+    <t>sheilangui@gmail.com</t>
+  </si>
+  <si>
+    <t>0795966792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muindi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elijah </t>
+  </si>
+  <si>
+    <t>emuindielijah@gmail.com</t>
+  </si>
+  <si>
+    <t>0792652184</t>
   </si>
 </sst>
 </file>
@@ -1385,7 +1409,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H74" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H76" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -3059,20 +3083,54 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="31">
+      <c r="A74" s="15">
         <v>45817.48228399306</v>
       </c>
-      <c r="B74" s="32" t="s">
+      <c r="B74" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="C74" s="32" t="s">
+      <c r="C74" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="E74" s="32" t="s">
+      <c r="E74" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="F74" s="33" t="s">
+      <c r="F74" s="17" t="s">
         <v>337</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10">
+        <v>45818.961079409724</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31">
+        <v>45819.27441445602</v>
+      </c>
+      <c r="B76" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="C76" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="E76" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="F76" s="33" t="s">
+        <v>345</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="350">
   <si>
     <t>Timestamp</t>
   </si>
@@ -1058,6 +1058,18 @@
   </si>
   <si>
     <t>0792652184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karanja </t>
+  </si>
+  <si>
+    <t>evagaka@gmail.com</t>
+  </si>
+  <si>
+    <t>0724992714</t>
   </si>
 </sst>
 </file>
@@ -1221,10 +1233,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1232,13 +1244,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1409,7 +1421,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H76" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H77" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -3117,20 +3129,38 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="31">
+      <c r="A76" s="15">
         <v>45819.27441445602</v>
       </c>
-      <c r="B76" s="32" t="s">
+      <c r="B76" s="16" t="s">
         <v>342</v>
       </c>
-      <c r="C76" s="32" t="s">
+      <c r="C76" s="16" t="s">
         <v>343</v>
       </c>
-      <c r="E76" s="32" t="s">
+      <c r="E76" s="16" t="s">
         <v>344</v>
       </c>
-      <c r="F76" s="33" t="s">
+      <c r="F76" s="17" t="s">
         <v>345</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31">
+        <v>45820.58295282407</v>
+      </c>
+      <c r="B77" s="32" t="s">
+        <v>346</v>
+      </c>
+      <c r="C77" s="32" t="s">
+        <v>347</v>
+      </c>
+      <c r="D77" s="32"/>
+      <c r="E77" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="F77" s="33" t="s">
+        <v>349</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="362">
   <si>
     <t>Timestamp</t>
   </si>
@@ -1066,10 +1066,46 @@
     <t xml:space="preserve">Karanja </t>
   </si>
   <si>
+    <t>Gatuota</t>
+  </si>
+  <si>
     <t>evagaka@gmail.com</t>
   </si>
   <si>
     <t>0724992714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victory </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muriuki </t>
+  </si>
+  <si>
+    <t>Victorymuthoni12@gmail.com</t>
+  </si>
+  <si>
+    <t>0724435821</t>
+  </si>
+  <si>
+    <t>Christine</t>
+  </si>
+  <si>
+    <t>Waweru</t>
+  </si>
+  <si>
+    <t>christinemumbi683@gmail.com</t>
+  </si>
+  <si>
+    <t>0748373291</t>
+  </si>
+  <si>
+    <t>Mutethya</t>
+  </si>
+  <si>
+    <t>joanmutethya@gmail.com</t>
+  </si>
+  <si>
+    <t>0729572814</t>
   </si>
 </sst>
 </file>
@@ -1233,10 +1269,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1244,13 +1280,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1421,7 +1457,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H77" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H80" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -3146,21 +3182,75 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="31">
+      <c r="A77" s="10">
         <v>45820.58295282407</v>
       </c>
-      <c r="B77" s="32" t="s">
+      <c r="B77" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="C77" s="32" t="s">
+      <c r="C77" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="D77" s="32"/>
-      <c r="E77" s="32" t="s">
+      <c r="D77" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="F77" s="33" t="s">
+      <c r="E77" s="11" t="s">
         <v>349</v>
+      </c>
+      <c r="F77" s="12" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="15">
+        <v>45824.50411851852</v>
+      </c>
+      <c r="B78" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="C78" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="E78" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="F78" s="17" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10">
+        <v>45824.61032503472</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31">
+        <v>45824.87789484954</v>
+      </c>
+      <c r="B80" s="32" t="s">
+        <v>331</v>
+      </c>
+      <c r="C80" s="32" t="s">
+        <v>359</v>
+      </c>
+      <c r="E80" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="F80" s="33" t="s">
+        <v>361</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="366">
   <si>
     <t>Timestamp</t>
   </si>
@@ -1093,6 +1093,9 @@
     <t>Waweru</t>
   </si>
   <si>
+    <t>Mumbi</t>
+  </si>
+  <si>
     <t>christinemumbi683@gmail.com</t>
   </si>
   <si>
@@ -1106,6 +1109,15 @@
   </si>
   <si>
     <t>0729572814</t>
+  </si>
+  <si>
+    <t>Caroline</t>
+  </si>
+  <si>
+    <t>Carolechege25@gmail.com</t>
+  </si>
+  <si>
+    <t>0722868711</t>
   </si>
 </sst>
 </file>
@@ -1269,10 +1281,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1280,13 +1292,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1457,7 +1469,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H80" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H81" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -3228,29 +3240,51 @@
       <c r="C79" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="D79" s="11"/>
+      <c r="D79" s="11" t="s">
+        <v>357</v>
+      </c>
       <c r="E79" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="31">
+      <c r="A80" s="15">
         <v>45824.87789484954</v>
       </c>
-      <c r="B80" s="32" t="s">
+      <c r="B80" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="C80" s="32" t="s">
-        <v>359</v>
-      </c>
-      <c r="E80" s="32" t="s">
+      <c r="C80" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="F80" s="33" t="s">
+      <c r="E80" s="16" t="s">
         <v>361</v>
+      </c>
+      <c r="F80" s="17" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31">
+        <v>45826.87335792824</v>
+      </c>
+      <c r="B81" s="32" t="s">
+        <v>363</v>
+      </c>
+      <c r="C81" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="D81" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="E81" s="32" t="s">
+        <v>364</v>
+      </c>
+      <c r="F81" s="33" t="s">
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="371">
   <si>
     <t>Timestamp</t>
   </si>
@@ -1118,6 +1118,21 @@
   </si>
   <si>
     <t>0722868711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zephyr </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gakundi </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>zephyrwaithira@gmail.com</t>
+  </si>
+  <si>
+    <t>0797147252</t>
   </si>
 </sst>
 </file>
@@ -1281,10 +1296,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1292,13 +1307,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1469,7 +1484,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H81" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H82" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -3268,23 +3283,43 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="31">
+      <c r="A81" s="10">
         <v>45826.87335792824</v>
       </c>
-      <c r="B81" s="32" t="s">
+      <c r="B81" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="C81" s="32" t="s">
+      <c r="C81" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="D81" s="32" t="s">
+      <c r="D81" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="E81" s="32" t="s">
+      <c r="E81" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="F81" s="33" t="s">
+      <c r="F81" s="12" t="s">
         <v>365</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31">
+        <v>45827.223707592595</v>
+      </c>
+      <c r="B82" s="32" t="s">
+        <v>366</v>
+      </c>
+      <c r="C82" s="32" t="s">
+        <v>367</v>
+      </c>
+      <c r="D82" s="32" t="s">
+        <v>368</v>
+      </c>
+      <c r="E82" s="32" t="s">
+        <v>369</v>
+      </c>
+      <c r="F82" s="33" t="s">
+        <v>370</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="382">
   <si>
     <t>Timestamp</t>
   </si>
@@ -1126,13 +1126,46 @@
     <t xml:space="preserve">Gakundi </t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>Waithira</t>
   </si>
   <si>
     <t>zephyrwaithira@gmail.com</t>
   </si>
   <si>
     <t>0797147252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ann </t>
+  </si>
+  <si>
+    <t>Ngugi</t>
+  </si>
+  <si>
+    <t>shirongugz@gmail.com</t>
+  </si>
+  <si>
+    <t>0711705960</t>
+  </si>
+  <si>
+    <t>Jessica</t>
+  </si>
+  <si>
+    <t>Wanjikuwanjiru24@gmail.com</t>
+  </si>
+  <si>
+    <t>0798907154</t>
+  </si>
+  <si>
+    <t>Gathere</t>
+  </si>
+  <si>
+    <t>Nyawira</t>
+  </si>
+  <si>
+    <t>mercygathere@gmail.com</t>
+  </si>
+  <si>
+    <t>0799807445</t>
   </si>
 </sst>
 </file>
@@ -1296,10 +1329,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1307,13 +1340,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1484,7 +1517,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H82" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H85" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -3303,23 +3336,80 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="31">
+      <c r="A82" s="15">
         <v>45827.223707592595</v>
       </c>
-      <c r="B82" s="32" t="s">
+      <c r="B82" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="C82" s="32" t="s">
+      <c r="C82" s="16" t="s">
         <v>367</v>
       </c>
-      <c r="D82" s="32" t="s">
+      <c r="D82" s="16" t="s">
         <v>368</v>
       </c>
-      <c r="E82" s="32" t="s">
+      <c r="E82" s="16" t="s">
         <v>369</v>
       </c>
-      <c r="F82" s="33" t="s">
+      <c r="F82" s="17" t="s">
         <v>370</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10">
+        <v>45831.002551111116</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="F83" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="15">
+        <v>45831.25448790509</v>
+      </c>
+      <c r="B84" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="C84" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="E84" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="F84" s="17" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="31">
+        <v>45831.82826292824</v>
+      </c>
+      <c r="B85" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C85" s="32" t="s">
+        <v>378</v>
+      </c>
+      <c r="D85" s="32" t="s">
+        <v>379</v>
+      </c>
+      <c r="E85" s="32" t="s">
+        <v>380</v>
+      </c>
+      <c r="F85" s="33" t="s">
+        <v>381</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="386">
   <si>
     <t>Timestamp</t>
   </si>
@@ -1166,6 +1166,18 @@
   </si>
   <si>
     <t>0799807445</t>
+  </si>
+  <si>
+    <t>Ann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Young </t>
+  </si>
+  <si>
+    <t>annyoung047@gmail.com</t>
+  </si>
+  <si>
+    <t>0702962148</t>
   </si>
 </sst>
 </file>
@@ -1329,10 +1341,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1340,13 +1352,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1517,7 +1529,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H85" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H86" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -3393,23 +3405,40 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="31">
+      <c r="A85" s="10">
         <v>45831.82826292824</v>
       </c>
-      <c r="B85" s="32" t="s">
+      <c r="B85" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C85" s="32" t="s">
+      <c r="C85" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="D85" s="32" t="s">
+      <c r="D85" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="E85" s="32" t="s">
+      <c r="E85" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="F85" s="33" t="s">
+      <c r="F85" s="12" t="s">
         <v>381</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="31">
+        <v>45841.6096583912</v>
+      </c>
+      <c r="B86" s="32" t="s">
+        <v>382</v>
+      </c>
+      <c r="C86" s="32" t="s">
+        <v>383</v>
+      </c>
+      <c r="E86" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="F86" s="33" t="s">
+        <v>385</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="391">
   <si>
     <t>Timestamp</t>
   </si>
@@ -1178,6 +1178,21 @@
   </si>
   <si>
     <t>0702962148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joyce </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Njuguna </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wambûi </t>
+  </si>
+  <si>
+    <t>jeenjuguna@yahoo.com</t>
+  </si>
+  <si>
+    <t>0720829905</t>
   </si>
 </sst>
 </file>
@@ -1341,10 +1356,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1352,13 +1367,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1529,7 +1544,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H86" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H87" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -3425,20 +3440,40 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="31">
+      <c r="A86" s="15">
         <v>45841.6096583912</v>
       </c>
-      <c r="B86" s="32" t="s">
+      <c r="B86" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="C86" s="32" t="s">
+      <c r="C86" s="16" t="s">
         <v>383</v>
       </c>
-      <c r="E86" s="32" t="s">
+      <c r="E86" s="16" t="s">
         <v>384</v>
       </c>
-      <c r="F86" s="33" t="s">
+      <c r="F86" s="17" t="s">
         <v>385</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="31">
+        <v>45843.49317686343</v>
+      </c>
+      <c r="B87" s="32" t="s">
+        <v>386</v>
+      </c>
+      <c r="C87" s="32" t="s">
+        <v>387</v>
+      </c>
+      <c r="D87" s="32" t="s">
+        <v>388</v>
+      </c>
+      <c r="E87" s="32" t="s">
+        <v>389</v>
+      </c>
+      <c r="F87" s="33" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/app/Console/Commands/Member/Member_Contacts.xlsx
+++ b/app/Console/Commands/Member/Member_Contacts.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="394">
   <si>
     <t>Timestamp</t>
   </si>
@@ -1193,6 +1193,15 @@
   </si>
   <si>
     <t>0720829905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chebet </t>
+  </si>
+  <si>
+    <t>Nancychebet1200@gmail.com</t>
+  </si>
+  <si>
+    <t>0795695004</t>
   </si>
 </sst>
 </file>
@@ -1356,10 +1365,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1367,13 +1376,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1544,7 +1553,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H87" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:H88" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="8">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="First Name" id="2"/>
@@ -3457,23 +3466,40 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="31">
+      <c r="A87" s="10">
         <v>45843.49317686343</v>
       </c>
-      <c r="B87" s="32" t="s">
+      <c r="B87" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="C87" s="32" t="s">
+      <c r="C87" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="D87" s="32" t="s">
+      <c r="D87" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="E87" s="32" t="s">
+      <c r="E87" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="F87" s="33" t="s">
+      <c r="F87" s="12" t="s">
         <v>390</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="31">
+        <v>45846.81186087963</v>
+      </c>
+      <c r="B88" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C88" s="32" t="s">
+        <v>391</v>
+      </c>
+      <c r="E88" s="32" t="s">
+        <v>392</v>
+      </c>
+      <c r="F88" s="33" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
